--- a/output/fluxos_amostra.xlsx
+++ b/output/fluxos_amostra.xlsx
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3546822.88</v>
+        <v>3545914.93</v>
       </c>
     </row>
     <row r="11">
@@ -606,7 +606,7 @@
         <v>278419.45</v>
       </c>
       <c r="D2" t="n">
-        <v>1020991.79</v>
+        <v>1020721.29</v>
       </c>
     </row>
     <row r="3">
@@ -622,7 +622,7 @@
         <v>194561.72</v>
       </c>
       <c r="D3" t="n">
-        <v>748247.2</v>
+        <v>748057.86</v>
       </c>
     </row>
     <row r="4">
@@ -638,7 +638,7 @@
         <v>171859.57</v>
       </c>
       <c r="D4" t="n">
-        <v>713410.47</v>
+        <v>713232.4300000001</v>
       </c>
     </row>
     <row r="5">
@@ -654,7 +654,7 @@
         <v>169963.48</v>
       </c>
       <c r="D5" t="n">
-        <v>667624.65</v>
+        <v>667455.28</v>
       </c>
     </row>
     <row r="6">
@@ -670,7 +670,7 @@
         <v>45846.49</v>
       </c>
       <c r="D6" t="n">
-        <v>177760.95</v>
+        <v>177713.77</v>
       </c>
     </row>
     <row r="7">
@@ -686,7 +686,7 @@
         <v>25504.66</v>
       </c>
       <c r="D7" t="n">
-        <v>111264.37</v>
+        <v>111238.29</v>
       </c>
     </row>
     <row r="8">
@@ -702,7 +702,7 @@
         <v>19432.36</v>
       </c>
       <c r="D8" t="n">
-        <v>81502.77</v>
+        <v>81482.09</v>
       </c>
     </row>
     <row r="9">
@@ -718,7 +718,7 @@
         <v>6319.76</v>
       </c>
       <c r="D9" t="n">
-        <v>26020.68</v>
+        <v>26013.92</v>
       </c>
     </row>
   </sheetData>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11877.5</v>
+        <v>11872.51</v>
       </c>
     </row>
     <row r="4">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13099.91</v>
+        <v>13095.36</v>
       </c>
     </row>
     <row r="6">
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19732.32</v>
+        <v>19725.45</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22075.84</v>
+        <v>22068.59</v>
       </c>
     </row>
     <row r="8">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32996.53</v>
+        <v>32985.66</v>
       </c>
     </row>
     <row r="9">
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34297.8</v>
+        <v>34286.5</v>
       </c>
     </row>
     <row r="10">
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>44644.69</v>
+        <v>44629.99</v>
       </c>
     </row>
     <row r="12">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>65931.28</v>
+        <v>65909.58</v>
       </c>
     </row>
     <row r="15">
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>67767.57000000001</v>
+        <v>67745.25999999999</v>
       </c>
     </row>
     <row r="16">
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>75761.22</v>
+        <v>75734.2</v>
       </c>
     </row>
     <row r="17">
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>76051.66</v>
+        <v>76022.50999999999</v>
       </c>
     </row>
     <row r="18">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>74551.88</v>
+        <v>74523.24000000001</v>
       </c>
     </row>
     <row r="19">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>85216.69</v>
+        <v>85182.45</v>
       </c>
     </row>
     <row r="21">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>94520.47</v>
+        <v>94482.46000000001</v>
       </c>
     </row>
     <row r="24">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>92428.72</v>
+        <v>92391.58</v>
       </c>
     </row>
     <row r="25">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>90335.53</v>
+        <v>90297.58</v>
       </c>
     </row>
     <row r="26">
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>88203.08</v>
+        <v>88164.5</v>
       </c>
     </row>
     <row r="27">
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>81240.84</v>
+        <v>81203.84</v>
       </c>
     </row>
     <row r="30">
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>76548.92999999999</v>
+        <v>76513.33</v>
       </c>
     </row>
     <row r="32">
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>74057.81</v>
+        <v>74024.73</v>
       </c>
     </row>
     <row r="33">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>71688.64999999999</v>
+        <v>71656.69</v>
       </c>
     </row>
     <row r="34">
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>69436.7</v>
+        <v>69406.95</v>
       </c>
     </row>
     <row r="35">
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>67177.34</v>
+        <v>67149.75999999999</v>
       </c>
     </row>
     <row r="36">
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>62845.76</v>
+        <v>62821.11</v>
       </c>
     </row>
     <row r="38">
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>60840.65</v>
+        <v>60818.41</v>
       </c>
     </row>
     <row r="39">
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>56913.19</v>
+        <v>56893.96</v>
       </c>
     </row>
     <row r="41">
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>51329.98</v>
+        <v>51314.51</v>
       </c>
     </row>
     <row r="44">
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>49559.37</v>
+        <v>49545.35</v>
       </c>
     </row>
     <row r="45">
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>47831.68</v>
+        <v>47818.61</v>
       </c>
     </row>
     <row r="46">
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>46116.94</v>
+        <v>46104.31</v>
       </c>
     </row>
     <row r="47">
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>44420.36</v>
+        <v>44408.27</v>
       </c>
     </row>
     <row r="48">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>42753.16</v>
+        <v>42741.5</v>
       </c>
     </row>
     <row r="49">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>38030.73</v>
+        <v>38020.3</v>
       </c>
     </row>
     <row r="52">
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>36506.49</v>
+        <v>36496.14</v>
       </c>
     </row>
     <row r="53">
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>34991.26</v>
+        <v>34980.67</v>
       </c>
     </row>
     <row r="54">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>33517.6</v>
+        <v>33506.89</v>
       </c>
     </row>
     <row r="55">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>32030.26</v>
+        <v>32020.01</v>
       </c>
     </row>
     <row r="56">
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>29168.26</v>
+        <v>29157.88</v>
       </c>
     </row>
     <row r="58">
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>25096.86</v>
+        <v>25087.04</v>
       </c>
     </row>
     <row r="61">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>23787.4</v>
+        <v>23778.06</v>
       </c>
     </row>
     <row r="62">
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>22568.6</v>
+        <v>22559.53</v>
       </c>
     </row>
     <row r="63">
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>21328.45</v>
+        <v>21319.69</v>
       </c>
     </row>
     <row r="64">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>20130.99</v>
+        <v>20122.7</v>
       </c>
     </row>
     <row r="65">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>17852.06</v>
+        <v>17844.76</v>
       </c>
     </row>
     <row r="67">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>15982.14</v>
+        <v>15975.59</v>
       </c>
     </row>
     <row r="69">
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>15070.23</v>
+        <v>15064.07</v>
       </c>
     </row>
     <row r="70">
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>14171.94</v>
+        <v>14165.98</v>
       </c>
     </row>
     <row r="71">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>13291.19</v>
+        <v>13285.4</v>
       </c>
     </row>
     <row r="72">
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>12465.89</v>
+        <v>12460.43</v>
       </c>
     </row>
     <row r="73">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>11651.04</v>
+        <v>11645.72</v>
       </c>
     </row>
     <row r="74">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>10177.52</v>
+        <v>10172.73</v>
       </c>
     </row>
     <row r="76">
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>8980.549999999999</v>
+        <v>8976</v>
       </c>
     </row>
     <row r="78">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>8386.5</v>
+        <v>8382.27</v>
       </c>
     </row>
     <row r="79">
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>7802.93</v>
+        <v>7798.84</v>
       </c>
     </row>
     <row r="80">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>7234.02</v>
+        <v>7230.22</v>
       </c>
     </row>
     <row r="81">
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>6711.42</v>
+        <v>6707.91</v>
       </c>
     </row>
     <row r="82">
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>5697.85</v>
+        <v>5694.86</v>
       </c>
     </row>
     <row r="84">
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4730.27</v>
+        <v>4727.79</v>
       </c>
     </row>
     <row r="86">
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4258.47</v>
+        <v>4256.23</v>
       </c>
     </row>
     <row r="87">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2966.76</v>
+        <v>2965.2</v>
       </c>
     </row>
     <row r="90">
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2280.55</v>
+        <v>2279.35</v>
       </c>
     </row>
     <row r="92">
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>2074.08</v>
+        <v>2072.99</v>
       </c>
     </row>
     <row r="93">
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1874.02</v>
+        <v>1873.04</v>
       </c>
     </row>
     <row r="94">
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1678.17</v>
+        <v>1677.3</v>
       </c>
     </row>
     <row r="95">
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1548.74</v>
+        <v>1547.96</v>
       </c>
     </row>
     <row r="96">
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1299.02</v>
+        <v>1298.39</v>
       </c>
     </row>
     <row r="98">
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1180.9</v>
+        <v>1180.36</v>
       </c>
     </row>
     <row r="99">
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1063.37</v>
+        <v>1062.92</v>
       </c>
     </row>
     <row r="100">
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>949.4400000000001</v>
+        <v>949.04</v>
       </c>
     </row>
     <row r="101">
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>836.49</v>
+        <v>836.17</v>
       </c>
     </row>
     <row r="102">
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>726.0599999999999</v>
+        <v>725.78</v>
       </c>
     </row>
     <row r="103">
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>617.42</v>
+        <v>617.2</v>
       </c>
     </row>
     <row r="104">
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>302.75</v>
+        <v>302.66</v>
       </c>
     </row>
     <row r="107">
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>99.8</v>
+        <v>99.77</v>
       </c>
     </row>
   </sheetData>
@@ -1971,7 +1971,7 @@
         <v>648.01</v>
       </c>
       <c r="K3" t="n">
-        <v>3251.69</v>
+        <v>3250.32</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
@@ -2055,7 +2055,7 @@
         <v>648.01</v>
       </c>
       <c r="K5" t="n">
-        <v>3201.33</v>
+        <v>3200.21</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         <v>648.01</v>
       </c>
       <c r="K6" t="n">
-        <v>3176.93</v>
+        <v>3175.82</v>
       </c>
       <c r="L6" t="b">
         <v>1</v>
@@ -2139,7 +2139,7 @@
         <v>648.01</v>
       </c>
       <c r="K7" t="n">
-        <v>3153.7</v>
+        <v>3152.66</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
@@ -2181,7 +2181,7 @@
         <v>648.01</v>
       </c>
       <c r="K8" t="n">
-        <v>3131.97</v>
+        <v>3130.94</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
@@ -2223,7 +2223,7 @@
         <v>634.51</v>
       </c>
       <c r="K9" t="n">
-        <v>3045.6</v>
+        <v>3044.59</v>
       </c>
       <c r="L9" t="b">
         <v>0</v>
@@ -2307,7 +2307,7 @@
         <v>607.51</v>
       </c>
       <c r="K11" t="n">
-        <v>2875.95</v>
+        <v>2875.01</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
@@ -2433,7 +2433,7 @@
         <v>567.01</v>
       </c>
       <c r="K14" t="n">
-        <v>2631.72</v>
+        <v>2630.86</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
@@ -2475,7 +2475,7 @@
         <v>553.51</v>
       </c>
       <c r="K15" t="n">
-        <v>2550.52</v>
+        <v>2549.69</v>
       </c>
       <c r="L15" t="b">
         <v>0</v>
@@ -2517,7 +2517,7 @@
         <v>540.01</v>
       </c>
       <c r="K16" t="n">
-        <v>2471.18</v>
+        <v>2470.3</v>
       </c>
       <c r="L16" t="b">
         <v>0</v>
@@ -2559,7 +2559,7 @@
         <v>526.51</v>
       </c>
       <c r="K17" t="n">
-        <v>2391.17</v>
+        <v>2390.26</v>
       </c>
       <c r="L17" t="b">
         <v>0</v>
@@ -2601,7 +2601,7 @@
         <v>513.01</v>
       </c>
       <c r="K18" t="n">
-        <v>2310.27</v>
+        <v>2309.38</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
@@ -2685,7 +2685,7 @@
         <v>486.01</v>
       </c>
       <c r="K20" t="n">
-        <v>2151.33</v>
+        <v>2150.46</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
@@ -2811,7 +2811,7 @@
         <v>445.5</v>
       </c>
       <c r="K23" t="n">
-        <v>1923.51</v>
+        <v>1922.74</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
@@ -2853,7 +2853,7 @@
         <v>432</v>
       </c>
       <c r="K24" t="n">
-        <v>1848.8</v>
+        <v>1848.06</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
@@ -2895,7 +2895,7 @@
         <v>418.5</v>
       </c>
       <c r="K25" t="n">
-        <v>1774.64</v>
+        <v>1773.9</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
@@ -2937,7 +2937,7 @@
         <v>405</v>
       </c>
       <c r="K26" t="n">
-        <v>1704.24</v>
+        <v>1703.5</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
@@ -3063,7 +3063,7 @@
         <v>364.5</v>
       </c>
       <c r="K29" t="n">
-        <v>1490.85</v>
+        <v>1490.17</v>
       </c>
       <c r="L29" t="b">
         <v>0</v>
@@ -3147,7 +3147,7 @@
         <v>337.5</v>
       </c>
       <c r="K31" t="n">
-        <v>1354.03</v>
+        <v>1353.4</v>
       </c>
       <c r="L31" t="b">
         <v>0</v>
@@ -3189,7 +3189,7 @@
         <v>324</v>
       </c>
       <c r="K32" t="n">
-        <v>1286.89</v>
+        <v>1286.31</v>
       </c>
       <c r="L32" t="b">
         <v>0</v>
@@ -3231,7 +3231,7 @@
         <v>310.5</v>
       </c>
       <c r="K33" t="n">
-        <v>1222.31</v>
+        <v>1221.77</v>
       </c>
       <c r="L33" t="b">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>297</v>
       </c>
       <c r="K34" t="n">
-        <v>1159.13</v>
+        <v>1158.63</v>
       </c>
       <c r="L34" t="b">
         <v>0</v>
@@ -3315,7 +3315,7 @@
         <v>283.5</v>
       </c>
       <c r="K35" t="n">
-        <v>1096.28</v>
+        <v>1095.83</v>
       </c>
       <c r="L35" t="b">
         <v>0</v>
@@ -3399,7 +3399,7 @@
         <v>256.5</v>
       </c>
       <c r="K37" t="n">
-        <v>974.46</v>
+        <v>974.08</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
@@ -3441,7 +3441,7 @@
         <v>243</v>
       </c>
       <c r="K38" t="n">
-        <v>916.46</v>
+        <v>916.13</v>
       </c>
       <c r="L38" t="b">
         <v>0</v>
@@ -3525,7 +3525,7 @@
         <v>216</v>
       </c>
       <c r="K40" t="n">
-        <v>802.91</v>
+        <v>802.64</v>
       </c>
       <c r="L40" t="b">
         <v>0</v>
@@ -3651,7 +3651,7 @@
         <v>175.5</v>
       </c>
       <c r="K43" t="n">
-        <v>639.11</v>
+        <v>638.92</v>
       </c>
       <c r="L43" t="b">
         <v>0</v>
@@ -3693,7 +3693,7 @@
         <v>162</v>
       </c>
       <c r="K44" t="n">
-        <v>586.35</v>
+        <v>586.1799999999999</v>
       </c>
       <c r="L44" t="b">
         <v>0</v>
@@ -3735,7 +3735,7 @@
         <v>148.5</v>
       </c>
       <c r="K45" t="n">
-        <v>534.46</v>
+        <v>534.3200000000001</v>
       </c>
       <c r="L45" t="b">
         <v>0</v>
@@ -3777,7 +3777,7 @@
         <v>135</v>
       </c>
       <c r="K46" t="n">
-        <v>483.09</v>
+        <v>482.96</v>
       </c>
       <c r="L46" t="b">
         <v>0</v>
@@ -3819,7 +3819,7 @@
         <v>121.5</v>
       </c>
       <c r="K47" t="n">
-        <v>432.29</v>
+        <v>432.17</v>
       </c>
       <c r="L47" t="b">
         <v>0</v>
@@ -3861,7 +3861,7 @@
         <v>108</v>
       </c>
       <c r="K48" t="n">
-        <v>382.16</v>
+        <v>382.05</v>
       </c>
       <c r="L48" t="b">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>67.5</v>
       </c>
       <c r="K51" t="n">
-        <v>234.9</v>
+        <v>234.83</v>
       </c>
       <c r="L51" t="b">
         <v>0</v>
@@ -4029,7 +4029,7 @@
         <v>54</v>
       </c>
       <c r="K52" t="n">
-        <v>186.81</v>
+        <v>186.75</v>
       </c>
       <c r="L52" t="b">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>40.5</v>
       </c>
       <c r="K53" t="n">
-        <v>139.25</v>
+        <v>139.2</v>
       </c>
       <c r="L53" t="b">
         <v>0</v>
@@ -4113,7 +4113,7 @@
         <v>27</v>
       </c>
       <c r="K54" t="n">
-        <v>92.23999999999999</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="L54" t="b">
         <v>0</v>
@@ -4155,7 +4155,7 @@
         <v>13.5</v>
       </c>
       <c r="K55" t="n">
-        <v>45.78</v>
+        <v>45.77</v>
       </c>
       <c r="L55" t="b">
         <v>0</v>
@@ -4197,7 +4197,7 @@
         <v>1718.98</v>
       </c>
       <c r="K56" t="n">
-        <v>8625.809999999999</v>
+        <v>8622.190000000001</v>
       </c>
       <c r="L56" t="b">
         <v>1</v>
@@ -4281,7 +4281,7 @@
         <v>1718.98</v>
       </c>
       <c r="K58" t="n">
-        <v>8492.219999999999</v>
+        <v>8489.27</v>
       </c>
       <c r="L58" t="b">
         <v>1</v>
@@ -4323,7 +4323,7 @@
         <v>1718.98</v>
       </c>
       <c r="K59" t="n">
-        <v>8427.49</v>
+        <v>8424.559999999999</v>
       </c>
       <c r="L59" t="b">
         <v>0</v>
@@ -4365,7 +4365,7 @@
         <v>1690.33</v>
       </c>
       <c r="K60" t="n">
-        <v>8226.450000000001</v>
+        <v>8223.75</v>
       </c>
       <c r="L60" t="b">
         <v>0</v>
@@ -4407,7 +4407,7 @@
         <v>1661.68</v>
       </c>
       <c r="K61" t="n">
-        <v>8031.31</v>
+        <v>8028.66</v>
       </c>
       <c r="L61" t="b">
         <v>0</v>
@@ -4449,7 +4449,7 @@
         <v>1633.03</v>
       </c>
       <c r="K62" t="n">
-        <v>7838.46</v>
+        <v>7835.88</v>
       </c>
       <c r="L62" t="b">
         <v>0</v>
@@ -4533,7 +4533,7 @@
         <v>1575.73</v>
       </c>
       <c r="K64" t="n">
-        <v>7459.56</v>
+        <v>7457.11</v>
       </c>
       <c r="L64" t="b">
         <v>0</v>
@@ -4659,7 +4659,7 @@
         <v>1489.78</v>
       </c>
       <c r="K67" t="n">
-        <v>6914.74</v>
+        <v>6912.46</v>
       </c>
       <c r="L67" t="b">
         <v>0</v>
@@ -4701,7 +4701,7 @@
         <v>1461.13</v>
       </c>
       <c r="K68" t="n">
-        <v>6732.82</v>
+        <v>6730.6</v>
       </c>
       <c r="L68" t="b">
         <v>0</v>
@@ -4743,7 +4743,7 @@
         <v>1432.48</v>
       </c>
       <c r="K69" t="n">
-        <v>6555.35</v>
+        <v>6553.01</v>
       </c>
       <c r="L69" t="b">
         <v>0</v>
@@ -4785,7 +4785,7 @@
         <v>1403.83</v>
       </c>
       <c r="K70" t="n">
-        <v>6375.64</v>
+        <v>6373.2</v>
       </c>
       <c r="L70" t="b">
         <v>0</v>
@@ -4827,7 +4827,7 @@
         <v>1375.18</v>
       </c>
       <c r="K71" t="n">
-        <v>6193.01</v>
+        <v>6190.63</v>
       </c>
       <c r="L71" t="b">
         <v>0</v>
@@ -4911,7 +4911,7 @@
         <v>1317.89</v>
       </c>
       <c r="K73" t="n">
-        <v>5833.69</v>
+        <v>5831.34</v>
       </c>
       <c r="L73" t="b">
         <v>0</v>
@@ -5037,7 +5037,7 @@
         <v>1231.94</v>
       </c>
       <c r="K76" t="n">
-        <v>5319.01</v>
+        <v>5316.87</v>
       </c>
       <c r="L76" t="b">
         <v>0</v>
@@ -5079,7 +5079,7 @@
         <v>1203.29</v>
       </c>
       <c r="K77" t="n">
-        <v>5149.56</v>
+        <v>5147.49</v>
       </c>
       <c r="L77" t="b">
         <v>0</v>
@@ -5121,7 +5121,7 @@
         <v>1174.64</v>
       </c>
       <c r="K78" t="n">
-        <v>4980.98</v>
+        <v>4978.89</v>
       </c>
       <c r="L78" t="b">
         <v>0</v>
@@ -5163,7 +5163,7 @@
         <v>1145.99</v>
       </c>
       <c r="K79" t="n">
-        <v>4822.27</v>
+        <v>4820.16</v>
       </c>
       <c r="L79" t="b">
         <v>0</v>
@@ -5289,7 +5289,7 @@
         <v>1060.04</v>
       </c>
       <c r="K82" t="n">
-        <v>4335.64</v>
+        <v>4333.67</v>
       </c>
       <c r="L82" t="b">
         <v>0</v>
@@ -5373,7 +5373,7 @@
         <v>1002.74</v>
       </c>
       <c r="K84" t="n">
-        <v>4022.89</v>
+        <v>4021.02</v>
       </c>
       <c r="L84" t="b">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>974.09</v>
       </c>
       <c r="K85" t="n">
-        <v>3868.92</v>
+        <v>3867.19</v>
       </c>
       <c r="L85" t="b">
         <v>0</v>
@@ -5457,7 +5457,7 @@
         <v>945.4400000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>3721.76</v>
+        <v>3720.1</v>
       </c>
       <c r="L86" t="b">
         <v>0</v>
@@ -5499,7 +5499,7 @@
         <v>916.79</v>
       </c>
       <c r="K87" t="n">
-        <v>3578</v>
+        <v>3576.47</v>
       </c>
       <c r="L87" t="b">
         <v>0</v>
@@ -5541,7 +5541,7 @@
         <v>888.14</v>
       </c>
       <c r="K88" t="n">
-        <v>3434.35</v>
+        <v>3432.94</v>
       </c>
       <c r="L88" t="b">
         <v>0</v>
@@ -5625,7 +5625,7 @@
         <v>830.84</v>
       </c>
       <c r="K90" t="n">
-        <v>3156.4</v>
+        <v>3155.16</v>
       </c>
       <c r="L90" t="b">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>802.1900000000001</v>
       </c>
       <c r="K91" t="n">
-        <v>3025.4</v>
+        <v>3024.29</v>
       </c>
       <c r="L91" t="b">
         <v>0</v>
@@ -5751,7 +5751,7 @@
         <v>744.89</v>
       </c>
       <c r="K93" t="n">
-        <v>2768.86</v>
+        <v>2767.93</v>
       </c>
       <c r="L93" t="b">
         <v>0</v>
@@ -5877,7 +5877,7 @@
         <v>658.9400000000001</v>
       </c>
       <c r="K96" t="n">
-        <v>2399.62</v>
+        <v>2398.9</v>
       </c>
       <c r="L96" t="b">
         <v>0</v>
@@ -5919,7 +5919,7 @@
         <v>630.29</v>
       </c>
       <c r="K97" t="n">
-        <v>2281.27</v>
+        <v>2280.63</v>
       </c>
       <c r="L97" t="b">
         <v>0</v>
@@ -5961,7 +5961,7 @@
         <v>601.64</v>
       </c>
       <c r="K98" t="n">
-        <v>2165.33</v>
+        <v>2164.74</v>
       </c>
       <c r="L98" t="b">
         <v>0</v>
@@ -6003,7 +6003,7 @@
         <v>572.99</v>
       </c>
       <c r="K99" t="n">
-        <v>2050.4</v>
+        <v>2049.84</v>
       </c>
       <c r="L99" t="b">
         <v>0</v>
@@ -6045,7 +6045,7 @@
         <v>544.34</v>
       </c>
       <c r="K100" t="n">
-        <v>1936.72</v>
+        <v>1936.2</v>
       </c>
       <c r="L100" t="b">
         <v>0</v>
@@ -6087,7 +6087,7 @@
         <v>515.6900000000001</v>
       </c>
       <c r="K101" t="n">
-        <v>1824.77</v>
+        <v>1824.27</v>
       </c>
       <c r="L101" t="b">
         <v>0</v>
@@ -6213,7 +6213,7 @@
         <v>429.75</v>
       </c>
       <c r="K104" t="n">
-        <v>1495.48</v>
+        <v>1495.07</v>
       </c>
       <c r="L104" t="b">
         <v>0</v>
@@ -6255,7 +6255,7 @@
         <v>401.1</v>
       </c>
       <c r="K105" t="n">
-        <v>1387.53</v>
+        <v>1387.13</v>
       </c>
       <c r="L105" t="b">
         <v>0</v>
@@ -6297,7 +6297,7 @@
         <v>372.45</v>
       </c>
       <c r="K106" t="n">
-        <v>1280.52</v>
+        <v>1280.13</v>
       </c>
       <c r="L106" t="b">
         <v>0</v>
@@ -6339,7 +6339,7 @@
         <v>343.8</v>
       </c>
       <c r="K107" t="n">
-        <v>1174.48</v>
+        <v>1174.11</v>
       </c>
       <c r="L107" t="b">
         <v>0</v>
@@ -6381,7 +6381,7 @@
         <v>315.15</v>
       </c>
       <c r="K108" t="n">
-        <v>1068.71</v>
+        <v>1068.37</v>
       </c>
       <c r="L108" t="b">
         <v>0</v>
@@ -6465,7 +6465,7 @@
         <v>257.85</v>
       </c>
       <c r="K110" t="n">
-        <v>861.85</v>
+        <v>861.55</v>
       </c>
       <c r="L110" t="b">
         <v>0</v>
@@ -6591,7 +6591,7 @@
         <v>171.9</v>
       </c>
       <c r="K113" t="n">
-        <v>561.47</v>
+        <v>561.25</v>
       </c>
       <c r="L113" t="b">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>143.25</v>
       </c>
       <c r="K114" t="n">
-        <v>463.87</v>
+        <v>463.69</v>
       </c>
       <c r="L114" t="b">
         <v>0</v>
@@ -6675,7 +6675,7 @@
         <v>114.6</v>
       </c>
       <c r="K115" t="n">
-        <v>368.45</v>
+        <v>368.3</v>
       </c>
       <c r="L115" t="b">
         <v>0</v>
@@ -6717,7 +6717,7 @@
         <v>85.95</v>
       </c>
       <c r="K116" t="n">
-        <v>273.88</v>
+        <v>273.77</v>
       </c>
       <c r="L116" t="b">
         <v>0</v>
@@ -6759,7 +6759,7 @@
         <v>57.3</v>
       </c>
       <c r="K117" t="n">
-        <v>181.17</v>
+        <v>181.1</v>
       </c>
       <c r="L117" t="b">
         <v>0</v>
@@ -6843,7 +6843,7 @@
         <v>284.67</v>
       </c>
       <c r="K119" t="n">
-        <v>1406.36</v>
+        <v>1405.88</v>
       </c>
       <c r="L119" t="b">
         <v>0</v>
@@ -6885,7 +6885,7 @@
         <v>276.77</v>
       </c>
       <c r="K120" t="n">
-        <v>1356.88</v>
+        <v>1356.4</v>
       </c>
       <c r="L120" t="b">
         <v>0</v>
@@ -6927,7 +6927,7 @@
         <v>268.86</v>
       </c>
       <c r="K121" t="n">
-        <v>1308.47</v>
+        <v>1308.04</v>
       </c>
       <c r="L121" t="b">
         <v>0</v>
@@ -6969,7 +6969,7 @@
         <v>260.95</v>
       </c>
       <c r="K122" t="n">
-        <v>1261.24</v>
+        <v>1260.82</v>
       </c>
       <c r="L122" t="b">
         <v>0</v>
@@ -7011,7 +7011,7 @@
         <v>253.04</v>
       </c>
       <c r="K123" t="n">
-        <v>1214.59</v>
+        <v>1214.19</v>
       </c>
       <c r="L123" t="b">
         <v>0</v>
@@ -7095,7 +7095,7 @@
         <v>237.23</v>
       </c>
       <c r="K125" t="n">
-        <v>1123.05</v>
+        <v>1122.68</v>
       </c>
       <c r="L125" t="b">
         <v>0</v>
@@ -7221,7 +7221,7 @@
         <v>213.51</v>
       </c>
       <c r="K128" t="n">
-        <v>990.97</v>
+        <v>990.65</v>
       </c>
       <c r="L128" t="b">
         <v>0</v>
@@ -7263,7 +7263,7 @@
         <v>205.6</v>
       </c>
       <c r="K129" t="n">
-        <v>947.38</v>
+        <v>947.0700000000001</v>
       </c>
       <c r="L129" t="b">
         <v>0</v>
@@ -7305,7 +7305,7 @@
         <v>197.69</v>
       </c>
       <c r="K130" t="n">
-        <v>904.67</v>
+        <v>904.35</v>
       </c>
       <c r="L130" t="b">
         <v>0</v>
@@ -7347,7 +7347,7 @@
         <v>189.78</v>
       </c>
       <c r="K131" t="n">
-        <v>861.91</v>
+        <v>861.58</v>
       </c>
       <c r="L131" t="b">
         <v>0</v>
@@ -7389,7 +7389,7 @@
         <v>181.87</v>
       </c>
       <c r="K132" t="n">
-        <v>819.0599999999999</v>
+        <v>818.74</v>
       </c>
       <c r="L132" t="b">
         <v>0</v>
@@ -7473,7 +7473,7 @@
         <v>166.06</v>
       </c>
       <c r="K134" t="n">
-        <v>735.0700000000001</v>
+        <v>734.78</v>
       </c>
       <c r="L134" t="b">
         <v>0</v>
@@ -7599,7 +7599,7 @@
         <v>142.34</v>
       </c>
       <c r="K137" t="n">
-        <v>614.55</v>
+        <v>614.3099999999999</v>
       </c>
       <c r="L137" t="b">
         <v>0</v>
@@ -7641,7 +7641,7 @@
         <v>134.43</v>
       </c>
       <c r="K138" t="n">
-        <v>575.3</v>
+        <v>575.0700000000001</v>
       </c>
       <c r="L138" t="b">
         <v>0</v>
@@ -7683,7 +7683,7 @@
         <v>126.52</v>
       </c>
       <c r="K139" t="n">
-        <v>536.51</v>
+        <v>536.28</v>
       </c>
       <c r="L139" t="b">
         <v>0</v>
@@ -7725,7 +7725,7 @@
         <v>118.61</v>
       </c>
       <c r="K140" t="n">
-        <v>499.12</v>
+        <v>498.91</v>
       </c>
       <c r="L140" t="b">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>94.89</v>
       </c>
       <c r="K143" t="n">
-        <v>388.11</v>
+        <v>387.94</v>
       </c>
       <c r="L143" t="b">
         <v>0</v>
@@ -7935,7 +7935,7 @@
         <v>79.08</v>
       </c>
       <c r="K145" t="n">
-        <v>317.25</v>
+        <v>317.1</v>
       </c>
       <c r="L145" t="b">
         <v>0</v>
@@ -7977,7 +7977,7 @@
         <v>71.17</v>
       </c>
       <c r="K146" t="n">
-        <v>282.67</v>
+        <v>282.54</v>
       </c>
       <c r="L146" t="b">
         <v>0</v>
@@ -8019,7 +8019,7 @@
         <v>63.26</v>
       </c>
       <c r="K147" t="n">
-        <v>249.03</v>
+        <v>248.92</v>
       </c>
       <c r="L147" t="b">
         <v>0</v>
@@ -8061,7 +8061,7 @@
         <v>55.35</v>
       </c>
       <c r="K148" t="n">
-        <v>216.03</v>
+        <v>215.94</v>
       </c>
       <c r="L148" t="b">
         <v>0</v>
@@ -8103,7 +8103,7 @@
         <v>47.45</v>
       </c>
       <c r="K149" t="n">
-        <v>183.47</v>
+        <v>183.39</v>
       </c>
       <c r="L149" t="b">
         <v>0</v>
@@ -8187,7 +8187,7 @@
         <v>31.63</v>
       </c>
       <c r="K151" t="n">
-        <v>120.17</v>
+        <v>120.12</v>
       </c>
       <c r="L151" t="b">
         <v>0</v>
@@ -8229,7 +8229,7 @@
         <v>23.72</v>
       </c>
       <c r="K152" t="n">
-        <v>89.47</v>
+        <v>89.44</v>
       </c>
       <c r="L152" t="b">
         <v>0</v>
@@ -8313,7 +8313,7 @@
         <v>7.91</v>
       </c>
       <c r="K154" t="n">
-        <v>29.39</v>
+        <v>29.38</v>
       </c>
       <c r="L154" t="b">
         <v>0</v>
@@ -8355,7 +8355,7 @@
         <v>1381.11</v>
       </c>
       <c r="K155" t="n">
-        <v>6771.02</v>
+        <v>6768.67</v>
       </c>
       <c r="L155" t="b">
         <v>1</v>
@@ -8397,7 +8397,7 @@
         <v>1381.11</v>
       </c>
       <c r="K156" t="n">
-        <v>6721.53</v>
+        <v>6719.32</v>
       </c>
       <c r="L156" t="b">
         <v>1</v>
@@ -8439,7 +8439,7 @@
         <v>1381.11</v>
       </c>
       <c r="K157" t="n">
-        <v>6675.22</v>
+        <v>6673.02</v>
       </c>
       <c r="L157" t="b">
         <v>1</v>
@@ -8481,7 +8481,7 @@
         <v>1381.11</v>
       </c>
       <c r="K158" t="n">
-        <v>6629.23</v>
+        <v>6627.05</v>
       </c>
       <c r="L158" t="b">
         <v>1</v>
@@ -8565,7 +8565,7 @@
         <v>1381.11</v>
       </c>
       <c r="K160" t="n">
-        <v>6538.2</v>
+        <v>6536.04</v>
       </c>
       <c r="L160" t="b">
         <v>1</v>
@@ -8691,7 +8691,7 @@
         <v>1381.11</v>
       </c>
       <c r="K163" t="n">
-        <v>6410.32</v>
+        <v>6408.21</v>
       </c>
       <c r="L163" t="b">
         <v>1</v>
@@ -8733,7 +8733,7 @@
         <v>1381.11</v>
       </c>
       <c r="K164" t="n">
-        <v>6364.06</v>
+        <v>6361.96</v>
       </c>
       <c r="L164" t="b">
         <v>1</v>
@@ -8775,7 +8775,7 @@
         <v>1381.11</v>
       </c>
       <c r="K165" t="n">
-        <v>6320.24</v>
+        <v>6317.98</v>
       </c>
       <c r="L165" t="b">
         <v>1</v>
@@ -8817,7 +8817,7 @@
         <v>1381.11</v>
       </c>
       <c r="K166" t="n">
-        <v>6272.42</v>
+        <v>6270.02</v>
       </c>
       <c r="L166" t="b">
         <v>1</v>
@@ -8859,7 +8859,7 @@
         <v>1381.11</v>
       </c>
       <c r="K167" t="n">
-        <v>6219.67</v>
+        <v>6217.29</v>
       </c>
       <c r="L167" t="b">
         <v>0</v>
@@ -8943,7 +8943,7 @@
         <v>1342.74</v>
       </c>
       <c r="K169" t="n">
-        <v>5943.72</v>
+        <v>5941.33</v>
       </c>
       <c r="L169" t="b">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>1285.2</v>
       </c>
       <c r="K172" t="n">
-        <v>5548.96</v>
+        <v>5546.73</v>
       </c>
       <c r="L172" t="b">
         <v>0</v>
@@ -9111,7 +9111,7 @@
         <v>1266.01</v>
       </c>
       <c r="K173" t="n">
-        <v>5418.01</v>
+        <v>5415.83</v>
       </c>
       <c r="L173" t="b">
         <v>0</v>
@@ -9153,7 +9153,7 @@
         <v>1246.83</v>
       </c>
       <c r="K174" t="n">
-        <v>5287.12</v>
+        <v>5284.9</v>
       </c>
       <c r="L174" t="b">
         <v>0</v>
@@ -9195,7 +9195,7 @@
         <v>1227.65</v>
       </c>
       <c r="K175" t="n">
-        <v>5165.91</v>
+        <v>5163.65</v>
       </c>
       <c r="L175" t="b">
         <v>0</v>
@@ -9321,7 +9321,7 @@
         <v>1170.1</v>
       </c>
       <c r="K178" t="n">
-        <v>4785.82</v>
+        <v>4783.64</v>
       </c>
       <c r="L178" t="b">
         <v>0</v>
@@ -9405,7 +9405,7 @@
         <v>1131.74</v>
       </c>
       <c r="K180" t="n">
-        <v>4540.43</v>
+        <v>4538.32</v>
       </c>
       <c r="L180" t="b">
         <v>0</v>
@@ -9447,7 +9447,7 @@
         <v>1112.56</v>
       </c>
       <c r="K181" t="n">
-        <v>4418.89</v>
+        <v>4416.92</v>
       </c>
       <c r="L181" t="b">
         <v>0</v>
@@ -9489,7 +9489,7 @@
         <v>1093.38</v>
       </c>
       <c r="K182" t="n">
-        <v>4304.12</v>
+        <v>4302.2</v>
       </c>
       <c r="L182" t="b">
         <v>0</v>
@@ -9531,7 +9531,7 @@
         <v>1074.19</v>
       </c>
       <c r="K183" t="n">
-        <v>4192.31</v>
+        <v>4190.52</v>
       </c>
       <c r="L183" t="b">
         <v>0</v>
@@ -9573,7 +9573,7 @@
         <v>1055.01</v>
       </c>
       <c r="K184" t="n">
-        <v>4079.63</v>
+        <v>4077.95</v>
       </c>
       <c r="L184" t="b">
         <v>0</v>
@@ -9657,7 +9657,7 @@
         <v>1016.65</v>
       </c>
       <c r="K186" t="n">
-        <v>3862.28</v>
+        <v>3860.77</v>
       </c>
       <c r="L186" t="b">
         <v>0</v>
@@ -9699,7 +9699,7 @@
         <v>997.47</v>
       </c>
       <c r="K187" t="n">
-        <v>3761.86</v>
+        <v>3760.48</v>
       </c>
       <c r="L187" t="b">
         <v>0</v>
@@ -9783,7 +9783,7 @@
         <v>959.1</v>
       </c>
       <c r="K189" t="n">
-        <v>3565.11</v>
+        <v>3563.9</v>
       </c>
       <c r="L189" t="b">
         <v>0</v>
@@ -9909,7 +9909,7 @@
         <v>901.5599999999999</v>
       </c>
       <c r="K192" t="n">
-        <v>3283.13</v>
+        <v>3282.14</v>
       </c>
       <c r="L192" t="b">
         <v>0</v>
@@ -9951,7 +9951,7 @@
         <v>882.37</v>
       </c>
       <c r="K193" t="n">
-        <v>3193.65</v>
+        <v>3192.75</v>
       </c>
       <c r="L193" t="b">
         <v>0</v>
@@ -9993,7 +9993,7 @@
         <v>863.1900000000001</v>
       </c>
       <c r="K194" t="n">
-        <v>3106.65</v>
+        <v>3105.8</v>
       </c>
       <c r="L194" t="b">
         <v>0</v>
@@ -10035,7 +10035,7 @@
         <v>844.01</v>
       </c>
       <c r="K195" t="n">
-        <v>3020.21</v>
+        <v>3019.38</v>
       </c>
       <c r="L195" t="b">
         <v>0</v>
@@ -10077,7 +10077,7 @@
         <v>824.83</v>
       </c>
       <c r="K196" t="n">
-        <v>2934.66</v>
+        <v>2933.86</v>
       </c>
       <c r="L196" t="b">
         <v>0</v>
@@ -10119,7 +10119,7 @@
         <v>805.65</v>
       </c>
       <c r="K197" t="n">
-        <v>2850.75</v>
+        <v>2849.98</v>
       </c>
       <c r="L197" t="b">
         <v>0</v>
@@ -10245,7 +10245,7 @@
         <v>748.1</v>
       </c>
       <c r="K200" t="n">
-        <v>2603.33</v>
+        <v>2602.62</v>
       </c>
       <c r="L200" t="b">
         <v>0</v>
@@ -10287,7 +10287,7 @@
         <v>728.92</v>
       </c>
       <c r="K201" t="n">
-        <v>2521.58</v>
+        <v>2520.86</v>
       </c>
       <c r="L201" t="b">
         <v>0</v>
@@ -10329,7 +10329,7 @@
         <v>709.74</v>
       </c>
       <c r="K202" t="n">
-        <v>2440.16</v>
+        <v>2439.42</v>
       </c>
       <c r="L202" t="b">
         <v>0</v>
@@ -10371,7 +10371,7 @@
         <v>690.55</v>
       </c>
       <c r="K203" t="n">
-        <v>2359.08</v>
+        <v>2358.33</v>
       </c>
       <c r="L203" t="b">
         <v>0</v>
@@ -10413,7 +10413,7 @@
         <v>671.37</v>
       </c>
       <c r="K204" t="n">
-        <v>2276.73</v>
+        <v>2276</v>
       </c>
       <c r="L204" t="b">
         <v>0</v>
@@ -10497,7 +10497,7 @@
         <v>633.01</v>
       </c>
       <c r="K206" t="n">
-        <v>2115.82</v>
+        <v>2115.07</v>
       </c>
       <c r="L206" t="b">
         <v>0</v>
@@ -10623,7 +10623,7 @@
         <v>575.46</v>
       </c>
       <c r="K209" t="n">
-        <v>1879.63</v>
+        <v>1878.9</v>
       </c>
       <c r="L209" t="b">
         <v>0</v>
@@ -10665,7 +10665,7 @@
         <v>556.28</v>
       </c>
       <c r="K210" t="n">
-        <v>1801.35</v>
+        <v>1800.65</v>
       </c>
       <c r="L210" t="b">
         <v>0</v>
@@ -10707,7 +10707,7 @@
         <v>537.1</v>
       </c>
       <c r="K211" t="n">
-        <v>1726.83</v>
+        <v>1726.14</v>
       </c>
       <c r="L211" t="b">
         <v>0</v>
@@ -10749,7 +10749,7 @@
         <v>517.91</v>
       </c>
       <c r="K212" t="n">
-        <v>1650.38</v>
+        <v>1649.7</v>
       </c>
       <c r="L212" t="b">
         <v>0</v>
@@ -10791,7 +10791,7 @@
         <v>498.73</v>
       </c>
       <c r="K213" t="n">
-        <v>1576.91</v>
+        <v>1576.26</v>
       </c>
       <c r="L213" t="b">
         <v>0</v>
@@ -10875,7 +10875,7 @@
         <v>460.37</v>
       </c>
       <c r="K215" t="n">
-        <v>1430.72</v>
+        <v>1430.14</v>
       </c>
       <c r="L215" t="b">
         <v>0</v>
@@ -10959,7 +10959,7 @@
         <v>422</v>
       </c>
       <c r="K217" t="n">
-        <v>1288.02</v>
+        <v>1287.49</v>
       </c>
       <c r="L217" t="b">
         <v>0</v>
@@ -11001,7 +11001,7 @@
         <v>402.82</v>
       </c>
       <c r="K218" t="n">
-        <v>1218.42</v>
+        <v>1217.92</v>
       </c>
       <c r="L218" t="b">
         <v>0</v>
@@ -11043,7 +11043,7 @@
         <v>383.64</v>
       </c>
       <c r="K219" t="n">
-        <v>1149.84</v>
+        <v>1149.36</v>
       </c>
       <c r="L219" t="b">
         <v>0</v>
@@ -11085,7 +11085,7 @@
         <v>364.46</v>
       </c>
       <c r="K220" t="n">
-        <v>1082.61</v>
+        <v>1082.14</v>
       </c>
       <c r="L220" t="b">
         <v>0</v>
@@ -11127,7 +11127,7 @@
         <v>345.28</v>
       </c>
       <c r="K221" t="n">
-        <v>1016.26</v>
+        <v>1015.81</v>
       </c>
       <c r="L221" t="b">
         <v>0</v>
@@ -11169,7 +11169,7 @@
         <v>326.09</v>
       </c>
       <c r="K222" t="n">
-        <v>950.74</v>
+        <v>950.3099999999999</v>
       </c>
       <c r="L222" t="b">
         <v>0</v>
@@ -11253,7 +11253,7 @@
         <v>287.73</v>
       </c>
       <c r="K224" t="n">
-        <v>823.33</v>
+        <v>822.95</v>
       </c>
       <c r="L224" t="b">
         <v>0</v>
@@ -11337,7 +11337,7 @@
         <v>249.37</v>
       </c>
       <c r="K226" t="n">
-        <v>699.72</v>
+        <v>699.37</v>
       </c>
       <c r="L226" t="b">
         <v>0</v>
@@ -11379,7 +11379,7 @@
         <v>230.18</v>
       </c>
       <c r="K227" t="n">
-        <v>638.72</v>
+        <v>638.4</v>
       </c>
       <c r="L227" t="b">
         <v>0</v>
@@ -11421,7 +11421,7 @@
         <v>211</v>
       </c>
       <c r="K228" t="n">
-        <v>578.87</v>
+        <v>578.5700000000001</v>
       </c>
       <c r="L228" t="b">
         <v>0</v>
@@ -11463,7 +11463,7 @@
         <v>191.82</v>
       </c>
       <c r="K229" t="n">
-        <v>520.48</v>
+        <v>520.2</v>
       </c>
       <c r="L229" t="b">
         <v>0</v>
@@ -11505,7 +11505,7 @@
         <v>172.64</v>
       </c>
       <c r="K230" t="n">
-        <v>463.29</v>
+        <v>463.05</v>
       </c>
       <c r="L230" t="b">
         <v>0</v>
@@ -11589,7 +11589,7 @@
         <v>134.27</v>
       </c>
       <c r="K232" t="n">
-        <v>352.48</v>
+        <v>352.29</v>
       </c>
       <c r="L232" t="b">
         <v>0</v>
@@ -11673,7 +11673,7 @@
         <v>95.91</v>
       </c>
       <c r="K234" t="n">
-        <v>246.53</v>
+        <v>246.41</v>
       </c>
       <c r="L234" t="b">
         <v>0</v>
@@ -11715,7 +11715,7 @@
         <v>76.73</v>
       </c>
       <c r="K235" t="n">
-        <v>195.06</v>
+        <v>194.96</v>
       </c>
       <c r="L235" t="b">
         <v>0</v>
@@ -11841,7 +11841,7 @@
         <v>19.18</v>
       </c>
       <c r="K238" t="n">
-        <v>47.18</v>
+        <v>47.15</v>
       </c>
       <c r="L238" t="b">
         <v>0</v>
@@ -11883,7 +11883,7 @@
         <v>547.73</v>
       </c>
       <c r="K239" t="n">
-        <v>2665.69</v>
+        <v>2664.82</v>
       </c>
       <c r="L239" t="b">
         <v>1</v>
@@ -11925,7 +11925,7 @@
         <v>547.73</v>
       </c>
       <c r="K240" t="n">
-        <v>2647.33</v>
+        <v>2646.46</v>
       </c>
       <c r="L240" t="b">
         <v>1</v>
@@ -11967,7 +11967,7 @@
         <v>547.73</v>
       </c>
       <c r="K241" t="n">
-        <v>2629.09</v>
+        <v>2628.22</v>
       </c>
       <c r="L241" t="b">
         <v>1</v>
@@ -12051,7 +12051,7 @@
         <v>547.73</v>
       </c>
       <c r="K243" t="n">
-        <v>2592.99</v>
+        <v>2592.13</v>
       </c>
       <c r="L243" t="b">
         <v>1</v>
@@ -12177,7 +12177,7 @@
         <v>536.3200000000001</v>
       </c>
       <c r="K246" t="n">
-        <v>2489.31</v>
+        <v>2488.49</v>
       </c>
       <c r="L246" t="b">
         <v>0</v>
@@ -12219,7 +12219,7 @@
         <v>524.91</v>
       </c>
       <c r="K247" t="n">
-        <v>2418.76</v>
+        <v>2417.97</v>
       </c>
       <c r="L247" t="b">
         <v>0</v>
@@ -12261,7 +12261,7 @@
         <v>513.5</v>
       </c>
       <c r="K248" t="n">
-        <v>2349.89</v>
+        <v>2349.05</v>
       </c>
       <c r="L248" t="b">
         <v>0</v>
@@ -12303,7 +12303,7 @@
         <v>502.09</v>
       </c>
       <c r="K249" t="n">
-        <v>2280.28</v>
+        <v>2279.41</v>
       </c>
       <c r="L249" t="b">
         <v>0</v>
@@ -12345,7 +12345,7 @@
         <v>490.68</v>
       </c>
       <c r="K250" t="n">
-        <v>2209.72</v>
+        <v>2208.87</v>
       </c>
       <c r="L250" t="b">
         <v>0</v>
@@ -12429,7 +12429,7 @@
         <v>467.86</v>
       </c>
       <c r="K252" t="n">
-        <v>2070.99</v>
+        <v>2070.16</v>
       </c>
       <c r="L252" t="b">
         <v>0</v>
@@ -12555,7 +12555,7 @@
         <v>433.62</v>
       </c>
       <c r="K255" t="n">
-        <v>1872.21</v>
+        <v>1871.46</v>
       </c>
       <c r="L255" t="b">
         <v>0</v>
@@ -12597,7 +12597,7 @@
         <v>422.21</v>
       </c>
       <c r="K256" t="n">
-        <v>1806.89</v>
+        <v>1806.16</v>
       </c>
       <c r="L256" t="b">
         <v>0</v>
@@ -12639,7 +12639,7 @@
         <v>410.8</v>
       </c>
       <c r="K257" t="n">
-        <v>1741.97</v>
+        <v>1741.24</v>
       </c>
       <c r="L257" t="b">
         <v>0</v>
@@ -12681,7 +12681,7 @@
         <v>399.39</v>
       </c>
       <c r="K258" t="n">
-        <v>1680.61</v>
+        <v>1679.88</v>
       </c>
       <c r="L258" t="b">
         <v>0</v>
@@ -12807,7 +12807,7 @@
         <v>365.16</v>
       </c>
       <c r="K261" t="n">
-        <v>1493.52</v>
+        <v>1492.84</v>
       </c>
       <c r="L261" t="b">
         <v>0</v>
@@ -12891,7 +12891,7 @@
         <v>342.33</v>
       </c>
       <c r="K263" t="n">
-        <v>1373.41</v>
+        <v>1372.77</v>
       </c>
       <c r="L263" t="b">
         <v>0</v>
@@ -12933,7 +12933,7 @@
         <v>330.92</v>
       </c>
       <c r="K264" t="n">
-        <v>1314.37</v>
+        <v>1313.78</v>
       </c>
       <c r="L264" t="b">
         <v>0</v>
@@ -12975,7 +12975,7 @@
         <v>319.51</v>
       </c>
       <c r="K265" t="n">
-        <v>1257.77</v>
+        <v>1257.21</v>
       </c>
       <c r="L265" t="b">
         <v>0</v>
@@ -13017,7 +13017,7 @@
         <v>308.1</v>
       </c>
       <c r="K266" t="n">
-        <v>1202.44</v>
+        <v>1201.92</v>
       </c>
       <c r="L266" t="b">
         <v>0</v>
@@ -13059,7 +13059,7 @@
         <v>296.69</v>
       </c>
       <c r="K267" t="n">
-        <v>1147.27</v>
+        <v>1146.8</v>
       </c>
       <c r="L267" t="b">
         <v>0</v>
@@ -13143,7 +13143,7 @@
         <v>273.87</v>
       </c>
       <c r="K269" t="n">
-        <v>1040.43</v>
+        <v>1040.02</v>
       </c>
       <c r="L269" t="b">
         <v>0</v>
@@ -13185,7 +13185,7 @@
         <v>262.46</v>
       </c>
       <c r="K270" t="n">
-        <v>989.83</v>
+        <v>989.47</v>
       </c>
       <c r="L270" t="b">
         <v>0</v>
@@ -13269,7 +13269,7 @@
         <v>239.63</v>
       </c>
       <c r="K272" t="n">
-        <v>890.75</v>
+        <v>890.45</v>
       </c>
       <c r="L272" t="b">
         <v>0</v>
@@ -13395,7 +13395,7 @@
         <v>205.4</v>
       </c>
       <c r="K275" t="n">
-        <v>747.99</v>
+        <v>747.76</v>
       </c>
       <c r="L275" t="b">
         <v>0</v>
@@ -13437,7 +13437,7 @@
         <v>193.99</v>
       </c>
       <c r="K276" t="n">
-        <v>702.12</v>
+        <v>701.92</v>
       </c>
       <c r="L276" t="b">
         <v>0</v>
@@ -13479,7 +13479,7 @@
         <v>182.58</v>
       </c>
       <c r="K277" t="n">
-        <v>657.1</v>
+        <v>656.92</v>
       </c>
       <c r="L277" t="b">
         <v>0</v>
@@ -13521,7 +13521,7 @@
         <v>171.17</v>
       </c>
       <c r="K278" t="n">
-        <v>612.5</v>
+        <v>612.34</v>
       </c>
       <c r="L278" t="b">
         <v>0</v>
@@ -13563,7 +13563,7 @@
         <v>159.76</v>
       </c>
       <c r="K279" t="n">
-        <v>568.4</v>
+        <v>568.24</v>
       </c>
       <c r="L279" t="b">
         <v>0</v>
@@ -13605,7 +13605,7 @@
         <v>148.34</v>
       </c>
       <c r="K280" t="n">
-        <v>524.91</v>
+        <v>524.77</v>
       </c>
       <c r="L280" t="b">
         <v>0</v>
@@ -13731,7 +13731,7 @@
         <v>114.11</v>
       </c>
       <c r="K283" t="n">
-        <v>397.1</v>
+        <v>396.99</v>
       </c>
       <c r="L283" t="b">
         <v>0</v>
@@ -13773,7 +13773,7 @@
         <v>102.7</v>
       </c>
       <c r="K284" t="n">
-        <v>355.27</v>
+        <v>355.17</v>
       </c>
       <c r="L284" t="b">
         <v>0</v>
@@ -13815,7 +13815,7 @@
         <v>91.29000000000001</v>
       </c>
       <c r="K285" t="n">
-        <v>313.86</v>
+        <v>313.77</v>
       </c>
       <c r="L285" t="b">
         <v>0</v>
@@ -13857,7 +13857,7 @@
         <v>79.88</v>
       </c>
       <c r="K286" t="n">
-        <v>272.88</v>
+        <v>272.79</v>
       </c>
       <c r="L286" t="b">
         <v>0</v>
@@ -13899,7 +13899,7 @@
         <v>68.47</v>
       </c>
       <c r="K287" t="n">
-        <v>232.18</v>
+        <v>232.11</v>
       </c>
       <c r="L287" t="b">
         <v>0</v>
@@ -13983,7 +13983,7 @@
         <v>45.64</v>
       </c>
       <c r="K289" t="n">
-        <v>152.57</v>
+        <v>152.51</v>
       </c>
       <c r="L289" t="b">
         <v>0</v>
@@ -14109,7 +14109,7 @@
         <v>11.41</v>
       </c>
       <c r="K292" t="n">
-        <v>37.27</v>
+        <v>37.26</v>
       </c>
       <c r="L292" t="b">
         <v>0</v>
@@ -14151,7 +14151,7 @@
         <v>2327.52</v>
       </c>
       <c r="K293" t="n">
-        <v>11249.46</v>
+        <v>11245.76</v>
       </c>
       <c r="L293" t="b">
         <v>1</v>
@@ -14193,7 +14193,7 @@
         <v>2327.52</v>
       </c>
       <c r="K294" t="n">
-        <v>11171.96</v>
+        <v>11168.28</v>
       </c>
       <c r="L294" t="b">
         <v>1</v>
@@ -14277,7 +14277,7 @@
         <v>2327.52</v>
       </c>
       <c r="K296" t="n">
-        <v>11018.54</v>
+        <v>11014.92</v>
       </c>
       <c r="L296" t="b">
         <v>1</v>
@@ -14403,7 +14403,7 @@
         <v>2327.52</v>
       </c>
       <c r="K299" t="n">
-        <v>10803.04</v>
+        <v>10799.48</v>
       </c>
       <c r="L299" t="b">
         <v>0</v>
@@ -14445,7 +14445,7 @@
         <v>2288.73</v>
       </c>
       <c r="K300" t="n">
-        <v>10546.33</v>
+        <v>10542.85</v>
       </c>
       <c r="L300" t="b">
         <v>0</v>
@@ -14487,7 +14487,7 @@
         <v>2249.94</v>
       </c>
       <c r="K301" t="n">
-        <v>10296.18</v>
+        <v>10292.51</v>
       </c>
       <c r="L301" t="b">
         <v>0</v>
@@ -14529,7 +14529,7 @@
         <v>2211.14</v>
       </c>
       <c r="K302" t="n">
-        <v>10042.11</v>
+        <v>10038.26</v>
       </c>
       <c r="L302" t="b">
         <v>0</v>
@@ -14571,7 +14571,7 @@
         <v>2172.35</v>
       </c>
       <c r="K303" t="n">
-        <v>9782.969999999999</v>
+        <v>9779.209999999999</v>
       </c>
       <c r="L303" t="b">
         <v>0</v>
@@ -14655,7 +14655,7 @@
         <v>2094.77</v>
       </c>
       <c r="K305" t="n">
-        <v>9272.6</v>
+        <v>9268.870000000001</v>
       </c>
       <c r="L305" t="b">
         <v>0</v>
@@ -14781,7 +14781,7 @@
         <v>1978.39</v>
       </c>
       <c r="K308" t="n">
-        <v>8541.91</v>
+        <v>8538.469999999999</v>
       </c>
       <c r="L308" t="b">
         <v>0</v>
@@ -14823,7 +14823,7 @@
         <v>1939.6</v>
       </c>
       <c r="K309" t="n">
-        <v>8300.67</v>
+        <v>8297.34</v>
       </c>
       <c r="L309" t="b">
         <v>0</v>
@@ -14865,7 +14865,7 @@
         <v>1900.81</v>
       </c>
       <c r="K310" t="n">
-        <v>8060.26</v>
+        <v>8056.88</v>
       </c>
       <c r="L310" t="b">
         <v>0</v>
@@ -14907,7 +14907,7 @@
         <v>1862.02</v>
       </c>
       <c r="K311" t="n">
-        <v>7835.3</v>
+        <v>7831.87</v>
       </c>
       <c r="L311" t="b">
         <v>0</v>
@@ -15033,7 +15033,7 @@
         <v>1745.64</v>
       </c>
       <c r="K314" t="n">
-        <v>7139.81</v>
+        <v>7136.56</v>
       </c>
       <c r="L314" t="b">
         <v>0</v>
@@ -15117,7 +15117,7 @@
         <v>1668.06</v>
       </c>
       <c r="K316" t="n">
-        <v>6692.08</v>
+        <v>6688.97</v>
       </c>
       <c r="L316" t="b">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>1629.26</v>
       </c>
       <c r="K317" t="n">
-        <v>6471.16</v>
+        <v>6468.27</v>
       </c>
       <c r="L317" t="b">
         <v>0</v>
@@ -15201,7 +15201,7 @@
         <v>1590.47</v>
       </c>
       <c r="K318" t="n">
-        <v>6260.96</v>
+        <v>6258.17</v>
       </c>
       <c r="L318" t="b">
         <v>0</v>
@@ -15243,7 +15243,7 @@
         <v>1551.68</v>
       </c>
       <c r="K319" t="n">
-        <v>6055.82</v>
+        <v>6053.23</v>
       </c>
       <c r="L319" t="b">
         <v>0</v>
@@ -15285,7 +15285,7 @@
         <v>1512.89</v>
       </c>
       <c r="K320" t="n">
-        <v>5850.19</v>
+        <v>5847.79</v>
       </c>
       <c r="L320" t="b">
         <v>0</v>
@@ -15369,7 +15369,7 @@
         <v>1435.3</v>
       </c>
       <c r="K322" t="n">
-        <v>5452.77</v>
+        <v>5450.63</v>
       </c>
       <c r="L322" t="b">
         <v>0</v>
@@ -15411,7 +15411,7 @@
         <v>1396.51</v>
       </c>
       <c r="K323" t="n">
-        <v>5266.83</v>
+        <v>5264.9</v>
       </c>
       <c r="L323" t="b">
         <v>0</v>
@@ -15495,7 +15495,7 @@
         <v>1318.93</v>
       </c>
       <c r="K325" t="n">
-        <v>4902.63</v>
+        <v>4900.97</v>
       </c>
       <c r="L325" t="b">
         <v>0</v>
@@ -15621,7 +15621,7 @@
         <v>1202.55</v>
       </c>
       <c r="K328" t="n">
-        <v>4379.24</v>
+        <v>4377.92</v>
       </c>
       <c r="L328" t="b">
         <v>0</v>
@@ -15663,7 +15663,7 @@
         <v>1163.76</v>
       </c>
       <c r="K329" t="n">
-        <v>4212.1</v>
+        <v>4210.9</v>
       </c>
       <c r="L329" t="b">
         <v>0</v>
@@ -15705,7 +15705,7 @@
         <v>1124.97</v>
       </c>
       <c r="K330" t="n">
-        <v>4048.79</v>
+        <v>4047.68</v>
       </c>
       <c r="L330" t="b">
         <v>0</v>
@@ -15747,7 +15747,7 @@
         <v>1086.18</v>
       </c>
       <c r="K331" t="n">
-        <v>3886.78</v>
+        <v>3885.71</v>
       </c>
       <c r="L331" t="b">
         <v>0</v>
@@ -15789,7 +15789,7 @@
         <v>1047.38</v>
       </c>
       <c r="K332" t="n">
-        <v>3726.49</v>
+        <v>3725.48</v>
       </c>
       <c r="L332" t="b">
         <v>0</v>
@@ -15831,7 +15831,7 @@
         <v>1008.59</v>
       </c>
       <c r="K333" t="n">
-        <v>3568.87</v>
+        <v>3567.9</v>
       </c>
       <c r="L333" t="b">
         <v>0</v>
@@ -15957,7 +15957,7 @@
         <v>892.22</v>
       </c>
       <c r="K336" t="n">
-        <v>3104.85</v>
+        <v>3103.99</v>
       </c>
       <c r="L336" t="b">
         <v>0</v>
@@ -15999,7 +15999,7 @@
         <v>853.42</v>
       </c>
       <c r="K337" t="n">
-        <v>2952.29</v>
+        <v>2951.45</v>
       </c>
       <c r="L337" t="b">
         <v>0</v>
@@ -16041,7 +16041,7 @@
         <v>814.63</v>
       </c>
       <c r="K338" t="n">
-        <v>2800.81</v>
+        <v>2799.96</v>
       </c>
       <c r="L338" t="b">
         <v>0</v>
@@ -16083,7 +16083,7 @@
         <v>775.84</v>
       </c>
       <c r="K339" t="n">
-        <v>2650.44</v>
+        <v>2649.59</v>
       </c>
       <c r="L339" t="b">
         <v>0</v>
@@ -16125,7 +16125,7 @@
         <v>737.05</v>
       </c>
       <c r="K340" t="n">
-        <v>2499.45</v>
+        <v>2498.65</v>
       </c>
       <c r="L340" t="b">
         <v>0</v>
@@ -16209,7 +16209,7 @@
         <v>659.46</v>
       </c>
       <c r="K342" t="n">
-        <v>2204.25</v>
+        <v>2203.47</v>
       </c>
       <c r="L342" t="b">
         <v>0</v>
@@ -16335,7 +16335,7 @@
         <v>543.09</v>
       </c>
       <c r="K345" t="n">
-        <v>1773.89</v>
+        <v>1773.2</v>
       </c>
       <c r="L345" t="b">
         <v>0</v>
@@ -16377,7 +16377,7 @@
         <v>504.3</v>
       </c>
       <c r="K346" t="n">
-        <v>1633.02</v>
+        <v>1632.38</v>
       </c>
       <c r="L346" t="b">
         <v>0</v>
@@ -16419,7 +16419,7 @@
         <v>465.5</v>
       </c>
       <c r="K347" t="n">
-        <v>1496.65</v>
+        <v>1496.05</v>
       </c>
       <c r="L347" t="b">
         <v>0</v>
@@ -16461,7 +16461,7 @@
         <v>426.71</v>
       </c>
       <c r="K348" t="n">
-        <v>1359.75</v>
+        <v>1359.2</v>
       </c>
       <c r="L348" t="b">
         <v>0</v>
@@ -16503,7 +16503,7 @@
         <v>387.92</v>
       </c>
       <c r="K349" t="n">
-        <v>1226.54</v>
+        <v>1226.03</v>
       </c>
       <c r="L349" t="b">
         <v>0</v>
@@ -16587,7 +16587,7 @@
         <v>310.34</v>
       </c>
       <c r="K351" t="n">
-        <v>964.45</v>
+        <v>964.0599999999999</v>
       </c>
       <c r="L351" t="b">
         <v>0</v>
@@ -16671,7 +16671,7 @@
         <v>232.75</v>
       </c>
       <c r="K353" t="n">
-        <v>710.39</v>
+        <v>710.1</v>
       </c>
       <c r="L353" t="b">
         <v>0</v>
@@ -16713,7 +16713,7 @@
         <v>193.96</v>
       </c>
       <c r="K354" t="n">
-        <v>586.67</v>
+        <v>586.4299999999999</v>
       </c>
       <c r="L354" t="b">
         <v>0</v>
@@ -16755,7 +16755,7 @@
         <v>155.17</v>
       </c>
       <c r="K355" t="n">
-        <v>465.07</v>
+        <v>464.87</v>
       </c>
       <c r="L355" t="b">
         <v>0</v>
@@ -16797,7 +16797,7 @@
         <v>116.38</v>
       </c>
       <c r="K356" t="n">
-        <v>345.69</v>
+        <v>345.54</v>
       </c>
       <c r="L356" t="b">
         <v>0</v>
@@ -16839,7 +16839,7 @@
         <v>77.58</v>
       </c>
       <c r="K357" t="n">
-        <v>228.35</v>
+        <v>228.25</v>
       </c>
       <c r="L357" t="b">
         <v>0</v>
@@ -16881,7 +16881,7 @@
         <v>38.79</v>
       </c>
       <c r="K358" t="n">
-        <v>113.1</v>
+        <v>113.05</v>
       </c>
       <c r="L358" t="b">
         <v>0</v>
@@ -16923,7 +16923,7 @@
         <v>368.52</v>
       </c>
       <c r="K359" t="n">
-        <v>1768.87</v>
+        <v>1768.29</v>
       </c>
       <c r="L359" t="b">
         <v>0</v>
@@ -17007,7 +17007,7 @@
         <v>337.81</v>
       </c>
       <c r="K361" t="n">
-        <v>1599.2</v>
+        <v>1598.67</v>
       </c>
       <c r="L361" t="b">
         <v>0</v>
@@ -17133,7 +17133,7 @@
         <v>291.74</v>
       </c>
       <c r="K364" t="n">
-        <v>1354.11</v>
+        <v>1353.67</v>
       </c>
       <c r="L364" t="b">
         <v>0</v>
@@ -17175,7 +17175,7 @@
         <v>276.39</v>
       </c>
       <c r="K365" t="n">
-        <v>1273.59</v>
+        <v>1273.17</v>
       </c>
       <c r="L365" t="b">
         <v>0</v>
@@ -17217,7 +17217,7 @@
         <v>261.03</v>
       </c>
       <c r="K366" t="n">
-        <v>1194.55</v>
+        <v>1194.12</v>
       </c>
       <c r="L366" t="b">
         <v>0</v>
@@ -17259,7 +17259,7 @@
         <v>245.68</v>
       </c>
       <c r="K367" t="n">
-        <v>1115.78</v>
+        <v>1115.35</v>
       </c>
       <c r="L367" t="b">
         <v>0</v>
@@ -17301,7 +17301,7 @@
         <v>230.32</v>
       </c>
       <c r="K368" t="n">
-        <v>1037.24</v>
+        <v>1036.85</v>
       </c>
       <c r="L368" t="b">
         <v>0</v>
@@ -17385,7 +17385,7 @@
         <v>199.61</v>
       </c>
       <c r="K370" t="n">
-        <v>883.6</v>
+        <v>883.25</v>
       </c>
       <c r="L370" t="b">
         <v>0</v>
@@ -17511,7 +17511,7 @@
         <v>153.55</v>
       </c>
       <c r="K373" t="n">
-        <v>662.97</v>
+        <v>662.7</v>
       </c>
       <c r="L373" t="b">
         <v>0</v>
@@ -17553,7 +17553,7 @@
         <v>138.19</v>
       </c>
       <c r="K374" t="n">
-        <v>591.42</v>
+        <v>591.1799999999999</v>
       </c>
       <c r="L374" t="b">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>122.84</v>
       </c>
       <c r="K375" t="n">
-        <v>520.89</v>
+        <v>520.6799999999999</v>
       </c>
       <c r="L375" t="b">
         <v>0</v>
@@ -17637,7 +17637,7 @@
         <v>107.48</v>
       </c>
       <c r="K376" t="n">
-        <v>452.29</v>
+        <v>452.09</v>
       </c>
       <c r="L376" t="b">
         <v>0</v>
@@ -17763,7 +17763,7 @@
         <v>61.42</v>
       </c>
       <c r="K379" t="n">
-        <v>251.21</v>
+        <v>251.1</v>
       </c>
       <c r="L379" t="b">
         <v>0</v>
@@ -17847,7 +17847,7 @@
         <v>30.71</v>
       </c>
       <c r="K381" t="n">
-        <v>123.21</v>
+        <v>123.15</v>
       </c>
       <c r="L381" t="b">
         <v>0</v>
@@ -17889,7 +17889,7 @@
         <v>15.35</v>
       </c>
       <c r="K382" t="n">
-        <v>60.99</v>
+        <v>60.96</v>
       </c>
       <c r="L382" t="b">
         <v>0</v>
@@ -17973,7 +17973,7 @@
         <v>972.01</v>
       </c>
       <c r="K384" t="n">
-        <v>4601.53</v>
+        <v>4600.01</v>
       </c>
       <c r="L384" t="b">
         <v>1</v>
@@ -18099,7 +18099,7 @@
         <v>945.01</v>
       </c>
       <c r="K387" t="n">
-        <v>4386.21</v>
+        <v>4384.76</v>
       </c>
       <c r="L387" t="b">
         <v>0</v>
@@ -18141,7 +18141,7 @@
         <v>918.01</v>
       </c>
       <c r="K388" t="n">
-        <v>4230.14</v>
+        <v>4228.75</v>
       </c>
       <c r="L388" t="b">
         <v>0</v>
@@ -18183,7 +18183,7 @@
         <v>891.01</v>
       </c>
       <c r="K389" t="n">
-        <v>4077.45</v>
+        <v>4076</v>
       </c>
       <c r="L389" t="b">
         <v>0</v>
@@ -18225,7 +18225,7 @@
         <v>864.01</v>
       </c>
       <c r="K390" t="n">
-        <v>3923.98</v>
+        <v>3922.47</v>
       </c>
       <c r="L390" t="b">
         <v>0</v>
@@ -18267,7 +18267,7 @@
         <v>837.01</v>
       </c>
       <c r="K391" t="n">
-        <v>3769.39</v>
+        <v>3767.94</v>
       </c>
       <c r="L391" t="b">
         <v>0</v>
@@ -18351,7 +18351,7 @@
         <v>783.01</v>
       </c>
       <c r="K393" t="n">
-        <v>3466.03</v>
+        <v>3464.64</v>
       </c>
       <c r="L393" t="b">
         <v>0</v>
@@ -18477,7 +18477,7 @@
         <v>702.01</v>
       </c>
       <c r="K396" t="n">
-        <v>3030.99</v>
+        <v>3029.77</v>
       </c>
       <c r="L396" t="b">
         <v>0</v>
@@ -18519,7 +18519,7 @@
         <v>675.01</v>
       </c>
       <c r="K397" t="n">
-        <v>2888.75</v>
+        <v>2887.59</v>
       </c>
       <c r="L397" t="b">
         <v>0</v>
@@ -18561,7 +18561,7 @@
         <v>648.01</v>
       </c>
       <c r="K398" t="n">
-        <v>2747.84</v>
+        <v>2746.68</v>
       </c>
       <c r="L398" t="b">
         <v>0</v>
@@ -18603,7 +18603,7 @@
         <v>621.01</v>
       </c>
       <c r="K399" t="n">
-        <v>2613.18</v>
+        <v>2612.03</v>
       </c>
       <c r="L399" t="b">
         <v>0</v>
@@ -18729,7 +18729,7 @@
         <v>540.01</v>
       </c>
       <c r="K402" t="n">
-        <v>2208.67</v>
+        <v>2207.66</v>
       </c>
       <c r="L402" t="b">
         <v>0</v>
@@ -18813,7 +18813,7 @@
         <v>486.01</v>
       </c>
       <c r="K404" t="n">
-        <v>1949.81</v>
+        <v>1948.9</v>
       </c>
       <c r="L404" t="b">
         <v>0</v>
@@ -18855,7 +18855,7 @@
         <v>459</v>
       </c>
       <c r="K405" t="n">
-        <v>1823.09</v>
+        <v>1822.28</v>
       </c>
       <c r="L405" t="b">
         <v>0</v>
@@ -18897,7 +18897,7 @@
         <v>432</v>
       </c>
       <c r="K406" t="n">
-        <v>1700.61</v>
+        <v>1699.85</v>
       </c>
       <c r="L406" t="b">
         <v>0</v>
@@ -18939,7 +18939,7 @@
         <v>405</v>
       </c>
       <c r="K407" t="n">
-        <v>1580.63</v>
+        <v>1579.96</v>
       </c>
       <c r="L407" t="b">
         <v>0</v>
@@ -18981,7 +18981,7 @@
         <v>378</v>
       </c>
       <c r="K408" t="n">
-        <v>1461.71</v>
+        <v>1461.11</v>
       </c>
       <c r="L408" t="b">
         <v>0</v>
@@ -19065,7 +19065,7 @@
         <v>324</v>
       </c>
       <c r="K410" t="n">
-        <v>1230.9</v>
+        <v>1230.42</v>
       </c>
       <c r="L410" t="b">
         <v>0</v>
@@ -19107,7 +19107,7 @@
         <v>297</v>
       </c>
       <c r="K411" t="n">
-        <v>1120.12</v>
+        <v>1119.71</v>
       </c>
       <c r="L411" t="b">
         <v>0</v>
@@ -19191,7 +19191,7 @@
         <v>243</v>
       </c>
       <c r="K413" t="n">
-        <v>903.27</v>
+        <v>902.97</v>
       </c>
       <c r="L413" t="b">
         <v>0</v>
@@ -19317,7 +19317,7 @@
         <v>162</v>
       </c>
       <c r="K416" t="n">
-        <v>589.95</v>
+        <v>589.77</v>
       </c>
       <c r="L416" t="b">
         <v>0</v>
@@ -19359,7 +19359,7 @@
         <v>135</v>
       </c>
       <c r="K417" t="n">
-        <v>488.62</v>
+        <v>488.48</v>
       </c>
       <c r="L417" t="b">
         <v>0</v>
@@ -19401,7 +19401,7 @@
         <v>108</v>
       </c>
       <c r="K418" t="n">
-        <v>388.7</v>
+        <v>388.59</v>
       </c>
       <c r="L418" t="b">
         <v>0</v>
@@ -19443,7 +19443,7 @@
         <v>81</v>
       </c>
       <c r="K419" t="n">
-        <v>289.85</v>
+        <v>289.77</v>
       </c>
       <c r="L419" t="b">
         <v>0</v>
@@ -19485,7 +19485,7 @@
         <v>54</v>
       </c>
       <c r="K420" t="n">
-        <v>192.13</v>
+        <v>192.08</v>
       </c>
       <c r="L420" t="b">
         <v>0</v>
@@ -19527,7 +19527,7 @@
         <v>27</v>
       </c>
       <c r="K421" t="n">
-        <v>95.54000000000001</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="L421" t="b">
         <v>0</v>
@@ -19569,7 +19569,7 @@
         <v>1443.94</v>
       </c>
       <c r="K422" t="n">
-        <v>6835.67</v>
+        <v>6833.42</v>
       </c>
       <c r="L422" t="b">
         <v>1</v>
@@ -19695,7 +19695,7 @@
         <v>1443.94</v>
       </c>
       <c r="K425" t="n">
-        <v>6701.98</v>
+        <v>6699.77</v>
       </c>
       <c r="L425" t="b">
         <v>1</v>
@@ -19737,7 +19737,7 @@
         <v>1443.94</v>
       </c>
       <c r="K426" t="n">
-        <v>6653.61</v>
+        <v>6651.42</v>
       </c>
       <c r="L426" t="b">
         <v>1</v>
@@ -19779,7 +19779,7 @@
         <v>1443.94</v>
       </c>
       <c r="K427" t="n">
-        <v>6607.79</v>
+        <v>6605.44</v>
       </c>
       <c r="L427" t="b">
         <v>1</v>
@@ -19821,7 +19821,7 @@
         <v>1443.94</v>
       </c>
       <c r="K428" t="n">
-        <v>6557.8</v>
+        <v>6555.29</v>
       </c>
       <c r="L428" t="b">
         <v>0</v>
@@ -19863,7 +19863,7 @@
         <v>1413.86</v>
       </c>
       <c r="K429" t="n">
-        <v>6367.19</v>
+        <v>6364.74</v>
       </c>
       <c r="L429" t="b">
         <v>0</v>
@@ -19947,7 +19947,7 @@
         <v>1353.7</v>
       </c>
       <c r="K431" t="n">
-        <v>5992.21</v>
+        <v>5989.8</v>
       </c>
       <c r="L431" t="b">
         <v>0</v>
@@ -20073,7 +20073,7 @@
         <v>1263.45</v>
       </c>
       <c r="K434" t="n">
-        <v>5455.08</v>
+        <v>5452.88</v>
       </c>
       <c r="L434" t="b">
         <v>0</v>
@@ -20115,7 +20115,7 @@
         <v>1233.37</v>
       </c>
       <c r="K435" t="n">
-        <v>5278.3</v>
+        <v>5276.18</v>
       </c>
       <c r="L435" t="b">
         <v>0</v>
@@ -20157,7 +20157,7 @@
         <v>1203.29</v>
       </c>
       <c r="K436" t="n">
-        <v>5102.47</v>
+        <v>5100.32</v>
       </c>
       <c r="L436" t="b">
         <v>0</v>
@@ -20199,7 +20199,7 @@
         <v>1173.2</v>
       </c>
       <c r="K437" t="n">
-        <v>4936.8</v>
+        <v>4934.64</v>
       </c>
       <c r="L437" t="b">
         <v>0</v>
@@ -20325,7 +20325,7 @@
         <v>1082.96</v>
       </c>
       <c r="K440" t="n">
-        <v>4429.39</v>
+        <v>4427.37</v>
       </c>
       <c r="L440" t="b">
         <v>0</v>
@@ -20409,7 +20409,7 @@
         <v>1022.79</v>
       </c>
       <c r="K442" t="n">
-        <v>4103.35</v>
+        <v>4101.44</v>
       </c>
       <c r="L442" t="b">
         <v>0</v>
@@ -20451,7 +20451,7 @@
         <v>992.71</v>
       </c>
       <c r="K443" t="n">
-        <v>3942.88</v>
+        <v>3941.12</v>
       </c>
       <c r="L443" t="b">
         <v>0</v>
@@ -20493,7 +20493,7 @@
         <v>962.63</v>
       </c>
       <c r="K444" t="n">
-        <v>3789.43</v>
+        <v>3787.74</v>
       </c>
       <c r="L444" t="b">
         <v>0</v>
@@ -20535,7 +20535,7 @@
         <v>932.55</v>
       </c>
       <c r="K445" t="n">
-        <v>3639.5</v>
+        <v>3637.94</v>
       </c>
       <c r="L445" t="b">
         <v>0</v>
@@ -20577,7 +20577,7 @@
         <v>902.46</v>
       </c>
       <c r="K446" t="n">
-        <v>3489.74</v>
+        <v>3488.31</v>
       </c>
       <c r="L446" t="b">
         <v>0</v>
@@ -20661,7 +20661,7 @@
         <v>842.3</v>
       </c>
       <c r="K448" t="n">
-        <v>3199.93</v>
+        <v>3198.68</v>
       </c>
       <c r="L448" t="b">
         <v>0</v>
@@ -20703,7 +20703,7 @@
         <v>812.22</v>
       </c>
       <c r="K449" t="n">
-        <v>3063.21</v>
+        <v>3062.09</v>
       </c>
       <c r="L449" t="b">
         <v>0</v>
@@ -20787,7 +20787,7 @@
         <v>752.05</v>
       </c>
       <c r="K451" t="n">
-        <v>2795.49</v>
+        <v>2794.54</v>
       </c>
       <c r="L451" t="b">
         <v>0</v>
@@ -20913,7 +20913,7 @@
         <v>661.8099999999999</v>
       </c>
       <c r="K454" t="n">
-        <v>2410.05</v>
+        <v>2409.33</v>
       </c>
       <c r="L454" t="b">
         <v>0</v>
@@ -20955,7 +20955,7 @@
         <v>631.73</v>
       </c>
       <c r="K455" t="n">
-        <v>2286.46</v>
+        <v>2285.81</v>
       </c>
       <c r="L455" t="b">
         <v>0</v>
@@ -20997,7 +20997,7 @@
         <v>601.64</v>
       </c>
       <c r="K456" t="n">
-        <v>2165.33</v>
+        <v>2164.74</v>
       </c>
       <c r="L456" t="b">
         <v>0</v>
@@ -21039,7 +21039,7 @@
         <v>571.5599999999999</v>
       </c>
       <c r="K457" t="n">
-        <v>2045.28</v>
+        <v>2044.72</v>
       </c>
       <c r="L457" t="b">
         <v>0</v>
@@ -21081,7 +21081,7 @@
         <v>541.48</v>
       </c>
       <c r="K458" t="n">
-        <v>1926.53</v>
+        <v>1926.01</v>
       </c>
       <c r="L458" t="b">
         <v>0</v>
@@ -21123,7 +21123,7 @@
         <v>511.4</v>
       </c>
       <c r="K459" t="n">
-        <v>1809.56</v>
+        <v>1809.07</v>
       </c>
       <c r="L459" t="b">
         <v>0</v>
@@ -21249,7 +21249,7 @@
         <v>421.15</v>
       </c>
       <c r="K462" t="n">
-        <v>1465.57</v>
+        <v>1465.17</v>
       </c>
       <c r="L462" t="b">
         <v>0</v>
@@ -21291,7 +21291,7 @@
         <v>391.07</v>
       </c>
       <c r="K463" t="n">
-        <v>1352.84</v>
+        <v>1352.46</v>
       </c>
       <c r="L463" t="b">
         <v>0</v>
@@ -21333,7 +21333,7 @@
         <v>360.99</v>
       </c>
       <c r="K464" t="n">
-        <v>1241.12</v>
+        <v>1240.74</v>
       </c>
       <c r="L464" t="b">
         <v>0</v>
@@ -21375,7 +21375,7 @@
         <v>330.9</v>
       </c>
       <c r="K465" t="n">
-        <v>1130.44</v>
+        <v>1130.08</v>
       </c>
       <c r="L465" t="b">
         <v>0</v>
@@ -21417,7 +21417,7 @@
         <v>300.82</v>
       </c>
       <c r="K466" t="n">
-        <v>1020.14</v>
+        <v>1019.81</v>
       </c>
       <c r="L466" t="b">
         <v>0</v>
@@ -21501,7 +21501,7 @@
         <v>240.66</v>
       </c>
       <c r="K468" t="n">
-        <v>804.4</v>
+        <v>804.11</v>
       </c>
       <c r="L468" t="b">
         <v>0</v>
@@ -21627,7 +21627,7 @@
         <v>150.41</v>
       </c>
       <c r="K471" t="n">
-        <v>491.29</v>
+        <v>491.1</v>
       </c>
       <c r="L471" t="b">
         <v>0</v>
@@ -21669,7 +21669,7 @@
         <v>120.33</v>
       </c>
       <c r="K472" t="n">
-        <v>389.65</v>
+        <v>389.5</v>
       </c>
       <c r="L472" t="b">
         <v>0</v>
@@ -21711,7 +21711,7 @@
         <v>90.25</v>
       </c>
       <c r="K473" t="n">
-        <v>290.15</v>
+        <v>290.04</v>
       </c>
       <c r="L473" t="b">
         <v>0</v>
@@ -21753,7 +21753,7 @@
         <v>60.16</v>
       </c>
       <c r="K474" t="n">
-        <v>191.72</v>
+        <v>191.64</v>
       </c>
       <c r="L474" t="b">
         <v>0</v>
@@ -21795,7 +21795,7 @@
         <v>30.08</v>
       </c>
       <c r="K475" t="n">
-        <v>95.11</v>
+        <v>95.08</v>
       </c>
       <c r="L475" t="b">
         <v>0</v>
@@ -21921,7 +21921,7 @@
         <v>194.43</v>
       </c>
       <c r="K478" t="n">
-        <v>902.45</v>
+        <v>902.15</v>
       </c>
       <c r="L478" t="b">
         <v>0</v>
@@ -21963,7 +21963,7 @@
         <v>185.59</v>
       </c>
       <c r="K479" t="n">
-        <v>855.21</v>
+        <v>854.9299999999999</v>
       </c>
       <c r="L479" t="b">
         <v>0</v>
@@ -22005,7 +22005,7 @@
         <v>176.76</v>
       </c>
       <c r="K480" t="n">
-        <v>808.88</v>
+        <v>808.59</v>
       </c>
       <c r="L480" t="b">
         <v>0</v>
@@ -22047,7 +22047,7 @@
         <v>167.92</v>
       </c>
       <c r="K481" t="n">
-        <v>762.62</v>
+        <v>762.33</v>
       </c>
       <c r="L481" t="b">
         <v>0</v>
@@ -22089,7 +22089,7 @@
         <v>159.08</v>
       </c>
       <c r="K482" t="n">
-        <v>716.41</v>
+        <v>716.13</v>
       </c>
       <c r="L482" t="b">
         <v>0</v>
@@ -22173,7 +22173,7 @@
         <v>141.41</v>
       </c>
       <c r="K484" t="n">
-        <v>625.9400000000001</v>
+        <v>625.6900000000001</v>
       </c>
       <c r="L484" t="b">
         <v>0</v>
@@ -22299,7 +22299,7 @@
         <v>114.89</v>
       </c>
       <c r="K487" t="n">
-        <v>496.06</v>
+        <v>495.86</v>
       </c>
       <c r="L487" t="b">
         <v>0</v>
@@ -22341,7 +22341,7 @@
         <v>106.05</v>
       </c>
       <c r="K488" t="n">
-        <v>453.87</v>
+        <v>453.68</v>
       </c>
       <c r="L488" t="b">
         <v>0</v>
@@ -22383,7 +22383,7 @@
         <v>97.22</v>
       </c>
       <c r="K489" t="n">
-        <v>412.24</v>
+        <v>412.07</v>
       </c>
       <c r="L489" t="b">
         <v>0</v>
@@ -22425,7 +22425,7 @@
         <v>88.38</v>
       </c>
       <c r="K490" t="n">
-        <v>371.89</v>
+        <v>371.73</v>
       </c>
       <c r="L490" t="b">
         <v>0</v>
@@ -22551,7 +22551,7 @@
         <v>61.86</v>
       </c>
       <c r="K493" t="n">
-        <v>253.03</v>
+        <v>252.92</v>
       </c>
       <c r="L493" t="b">
         <v>0</v>
@@ -22635,7 +22635,7 @@
         <v>44.19</v>
       </c>
       <c r="K495" t="n">
-        <v>177.28</v>
+        <v>177.2</v>
       </c>
       <c r="L495" t="b">
         <v>0</v>
@@ -22677,7 +22677,7 @@
         <v>35.35</v>
       </c>
       <c r="K496" t="n">
-        <v>140.41</v>
+        <v>140.35</v>
       </c>
       <c r="L496" t="b">
         <v>0</v>
@@ -22719,7 +22719,7 @@
         <v>26.51</v>
       </c>
       <c r="K497" t="n">
-        <v>104.37</v>
+        <v>104.33</v>
       </c>
       <c r="L497" t="b">
         <v>0</v>
@@ -22761,7 +22761,7 @@
         <v>17.68</v>
       </c>
       <c r="K498" t="n">
-        <v>68.98</v>
+        <v>68.95</v>
       </c>
       <c r="L498" t="b">
         <v>0</v>
@@ -22803,7 +22803,7 @@
         <v>8.84</v>
       </c>
       <c r="K499" t="n">
-        <v>34.18</v>
+        <v>34.16</v>
       </c>
       <c r="L499" t="b">
         <v>0</v>
@@ -22887,7 +22887,7 @@
         <v>4036.94</v>
       </c>
       <c r="K501" t="n">
-        <v>18737.21</v>
+        <v>18731.05</v>
       </c>
       <c r="L501" t="b">
         <v>1</v>
@@ -22929,7 +22929,7 @@
         <v>4036.94</v>
       </c>
       <c r="K502" t="n">
-        <v>18602</v>
+        <v>18595.87</v>
       </c>
       <c r="L502" t="b">
         <v>1</v>
@@ -22971,7 +22971,7 @@
         <v>4036.94</v>
       </c>
       <c r="K503" t="n">
-        <v>18473.9</v>
+        <v>18467.32</v>
       </c>
       <c r="L503" t="b">
         <v>1</v>
@@ -23013,7 +23013,7 @@
         <v>4036.94</v>
       </c>
       <c r="K504" t="n">
-        <v>18334.14</v>
+        <v>18327.11</v>
       </c>
       <c r="L504" t="b">
         <v>1</v>
@@ -23055,7 +23055,7 @@
         <v>4036.94</v>
       </c>
       <c r="K505" t="n">
-        <v>18179.96</v>
+        <v>18172.98</v>
       </c>
       <c r="L505" t="b">
         <v>1</v>
@@ -23139,7 +23139,7 @@
         <v>4036.94</v>
       </c>
       <c r="K507" t="n">
-        <v>17869.73</v>
+        <v>17862.55</v>
       </c>
       <c r="L507" t="b">
         <v>1</v>
@@ -23265,7 +23265,7 @@
         <v>4036.94</v>
       </c>
       <c r="K510" t="n">
-        <v>17429.9</v>
+        <v>17422.89</v>
       </c>
       <c r="L510" t="b">
         <v>1</v>
@@ -23307,7 +23307,7 @@
         <v>4036.94</v>
       </c>
       <c r="K511" t="n">
-        <v>17276.41</v>
+        <v>17269.47</v>
       </c>
       <c r="L511" t="b">
         <v>1</v>
@@ -23349,7 +23349,7 @@
         <v>4036.94</v>
       </c>
       <c r="K512" t="n">
-        <v>17118.41</v>
+        <v>17111.22</v>
       </c>
       <c r="L512" t="b">
         <v>0</v>
@@ -23391,7 +23391,7 @@
         <v>3988.88</v>
       </c>
       <c r="K513" t="n">
-        <v>16785.08</v>
+        <v>16777.73</v>
       </c>
       <c r="L513" t="b">
         <v>0</v>
@@ -23517,7 +23517,7 @@
         <v>3844.71</v>
       </c>
       <c r="K516" t="n">
-        <v>15725.17</v>
+        <v>15718</v>
       </c>
       <c r="L516" t="b">
         <v>0</v>
@@ -23601,7 +23601,7 @@
         <v>3748.59</v>
       </c>
       <c r="K518" t="n">
-        <v>15038.97</v>
+        <v>15031.98</v>
       </c>
       <c r="L518" t="b">
         <v>0</v>
@@ -23643,7 +23643,7 @@
         <v>3700.53</v>
       </c>
       <c r="K519" t="n">
-        <v>14697.87</v>
+        <v>14691.31</v>
       </c>
       <c r="L519" t="b">
         <v>0</v>
@@ -23685,7 +23685,7 @@
         <v>3652.47</v>
       </c>
       <c r="K520" t="n">
-        <v>14378.11</v>
+        <v>14371.7</v>
       </c>
       <c r="L520" t="b">
         <v>0</v>
@@ -23727,7 +23727,7 @@
         <v>3604.41</v>
       </c>
       <c r="K521" t="n">
-        <v>14067.13</v>
+        <v>14061.11</v>
       </c>
       <c r="L521" t="b">
         <v>0</v>
@@ -23769,7 +23769,7 @@
         <v>3556.35</v>
       </c>
       <c r="K522" t="n">
-        <v>13752.07</v>
+        <v>13746.43</v>
       </c>
       <c r="L522" t="b">
         <v>0</v>
@@ -23853,7 +23853,7 @@
         <v>3460.23</v>
       </c>
       <c r="K524" t="n">
-        <v>13145.57</v>
+        <v>13140.41</v>
       </c>
       <c r="L524" t="b">
         <v>0</v>
@@ -23895,7 +23895,7 @@
         <v>3412.18</v>
       </c>
       <c r="K525" t="n">
-        <v>12868.74</v>
+        <v>12864.03</v>
       </c>
       <c r="L525" t="b">
         <v>0</v>
@@ -23979,7 +23979,7 @@
         <v>3316.06</v>
       </c>
       <c r="K527" t="n">
-        <v>12326.24</v>
+        <v>12322.07</v>
       </c>
       <c r="L527" t="b">
         <v>0</v>
@@ -24105,7 +24105,7 @@
         <v>3171.88</v>
       </c>
       <c r="K530" t="n">
-        <v>11550.81</v>
+        <v>11547.32</v>
       </c>
       <c r="L530" t="b">
         <v>0</v>
@@ -24147,7 +24147,7 @@
         <v>3123.82</v>
       </c>
       <c r="K531" t="n">
-        <v>11306.32</v>
+        <v>11303.12</v>
       </c>
       <c r="L531" t="b">
         <v>0</v>
@@ -24189,7 +24189,7 @@
         <v>3075.76</v>
       </c>
       <c r="K532" t="n">
-        <v>11069.77</v>
+        <v>11066.74</v>
       </c>
       <c r="L532" t="b">
         <v>0</v>
@@ -24231,7 +24231,7 @@
         <v>3027.71</v>
       </c>
       <c r="K533" t="n">
-        <v>10834.36</v>
+        <v>10831.39</v>
       </c>
       <c r="L533" t="b">
         <v>0</v>
@@ -24273,7 +24273,7 @@
         <v>2979.65</v>
       </c>
       <c r="K534" t="n">
-        <v>10601.3</v>
+        <v>10598.41</v>
       </c>
       <c r="L534" t="b">
         <v>0</v>
@@ -24315,7 +24315,7 @@
         <v>2931.59</v>
       </c>
       <c r="K535" t="n">
-        <v>10373.34</v>
+        <v>10370.51</v>
       </c>
       <c r="L535" t="b">
         <v>0</v>
@@ -24441,7 +24441,7 @@
         <v>2787.41</v>
       </c>
       <c r="K538" t="n">
-        <v>9699.99</v>
+        <v>9697.33</v>
       </c>
       <c r="L538" t="b">
         <v>0</v>
@@ -24483,7 +24483,7 @@
         <v>2739.35</v>
       </c>
       <c r="K539" t="n">
-        <v>9476.360000000001</v>
+        <v>9473.68</v>
       </c>
       <c r="L539" t="b">
         <v>0</v>
@@ -24525,7 +24525,7 @@
         <v>2691.29</v>
       </c>
       <c r="K540" t="n">
-        <v>9253.01</v>
+        <v>9250.219999999999</v>
       </c>
       <c r="L540" t="b">
         <v>0</v>
@@ -24567,7 +24567,7 @@
         <v>2643.23</v>
       </c>
       <c r="K541" t="n">
-        <v>9029.879999999999</v>
+        <v>9026.99</v>
       </c>
       <c r="L541" t="b">
         <v>0</v>
@@ -24609,7 +24609,7 @@
         <v>2595.18</v>
       </c>
       <c r="K542" t="n">
-        <v>8800.68</v>
+        <v>8797.860000000001</v>
       </c>
       <c r="L542" t="b">
         <v>0</v>
@@ -24693,7 +24693,7 @@
         <v>2499.06</v>
       </c>
       <c r="K544" t="n">
-        <v>8353.09</v>
+        <v>8350.120000000001</v>
       </c>
       <c r="L544" t="b">
         <v>0</v>
@@ -24819,7 +24819,7 @@
         <v>2354.88</v>
       </c>
       <c r="K547" t="n">
-        <v>7691.77</v>
+        <v>7688.76</v>
       </c>
       <c r="L547" t="b">
         <v>0</v>
@@ -24861,7 +24861,7 @@
         <v>2306.82</v>
       </c>
       <c r="K548" t="n">
-        <v>7470</v>
+        <v>7467.06</v>
       </c>
       <c r="L548" t="b">
         <v>0</v>
@@ -24903,7 +24903,7 @@
         <v>2258.76</v>
       </c>
       <c r="K549" t="n">
-        <v>7262.21</v>
+        <v>7259.29</v>
       </c>
       <c r="L549" t="b">
         <v>0</v>
@@ -24945,7 +24945,7 @@
         <v>2210.71</v>
       </c>
       <c r="K550" t="n">
-        <v>7044.61</v>
+        <v>7041.71</v>
       </c>
       <c r="L550" t="b">
         <v>0</v>
@@ -24987,7 +24987,7 @@
         <v>2162.65</v>
       </c>
       <c r="K551" t="n">
-        <v>6837.92</v>
+        <v>6835.11</v>
       </c>
       <c r="L551" t="b">
         <v>0</v>
@@ -25071,7 +25071,7 @@
         <v>2066.53</v>
       </c>
       <c r="K553" t="n">
-        <v>6422.31</v>
+        <v>6419.67</v>
       </c>
       <c r="L553" t="b">
         <v>0</v>
@@ -25155,7 +25155,7 @@
         <v>1970.41</v>
       </c>
       <c r="K555" t="n">
-        <v>6013.97</v>
+        <v>6011.5</v>
       </c>
       <c r="L555" t="b">
         <v>0</v>
@@ -25197,7 +25197,7 @@
         <v>1922.35</v>
       </c>
       <c r="K556" t="n">
-        <v>5814.53</v>
+        <v>5812.14</v>
       </c>
       <c r="L556" t="b">
         <v>0</v>
@@ -25239,7 +25239,7 @@
         <v>1874.29</v>
       </c>
       <c r="K557" t="n">
-        <v>5617.59</v>
+        <v>5615.23</v>
       </c>
       <c r="L557" t="b">
         <v>0</v>
@@ -25281,7 +25281,7 @@
         <v>1826.24</v>
       </c>
       <c r="K558" t="n">
-        <v>5424.77</v>
+        <v>5422.4</v>
       </c>
       <c r="L558" t="b">
         <v>0</v>
@@ -25323,7 +25323,7 @@
         <v>1778.18</v>
       </c>
       <c r="K559" t="n">
-        <v>5233.73</v>
+        <v>5231.44</v>
       </c>
       <c r="L559" t="b">
         <v>0</v>
@@ -25365,7 +25365,7 @@
         <v>1730.12</v>
       </c>
       <c r="K560" t="n">
-        <v>5044.21</v>
+        <v>5041.91</v>
       </c>
       <c r="L560" t="b">
         <v>0</v>
@@ -25449,7 +25449,7 @@
         <v>1634</v>
       </c>
       <c r="K562" t="n">
-        <v>4675.66</v>
+        <v>4673.45</v>
       </c>
       <c r="L562" t="b">
         <v>0</v>
@@ -25533,7 +25533,7 @@
         <v>1537.88</v>
       </c>
       <c r="K564" t="n">
-        <v>4315.31</v>
+        <v>4313.12</v>
       </c>
       <c r="L564" t="b">
         <v>0</v>
@@ -25575,7 +25575,7 @@
         <v>1489.82</v>
       </c>
       <c r="K565" t="n">
-        <v>4134.02</v>
+        <v>4131.92</v>
       </c>
       <c r="L565" t="b">
         <v>0</v>
@@ -25617,7 +25617,7 @@
         <v>1441.76</v>
       </c>
       <c r="K566" t="n">
-        <v>3955.39</v>
+        <v>3953.32</v>
       </c>
       <c r="L566" t="b">
         <v>0</v>
@@ -25659,7 +25659,7 @@
         <v>1393.71</v>
       </c>
       <c r="K567" t="n">
-        <v>3781.61</v>
+        <v>3779.62</v>
       </c>
       <c r="L567" t="b">
         <v>0</v>
@@ -25701,7 +25701,7 @@
         <v>1345.65</v>
       </c>
       <c r="K568" t="n">
-        <v>3611.16</v>
+        <v>3609.27</v>
       </c>
       <c r="L568" t="b">
         <v>0</v>
@@ -25785,7 +25785,7 @@
         <v>1249.53</v>
       </c>
       <c r="K570" t="n">
-        <v>3280.07</v>
+        <v>3278.35</v>
       </c>
       <c r="L570" t="b">
         <v>0</v>
@@ -25869,7 +25869,7 @@
         <v>1153.41</v>
       </c>
       <c r="K572" t="n">
-        <v>2964.82</v>
+        <v>2963.26</v>
       </c>
       <c r="L572" t="b">
         <v>0</v>
@@ -25911,7 +25911,7 @@
         <v>1105.35</v>
       </c>
       <c r="K573" t="n">
-        <v>2810.12</v>
+        <v>2808.64</v>
       </c>
       <c r="L573" t="b">
         <v>0</v>
@@ -26037,7 +26037,7 @@
         <v>961.1799999999999</v>
       </c>
       <c r="K576" t="n">
-        <v>2364.06</v>
+        <v>2362.82</v>
       </c>
       <c r="L576" t="b">
         <v>0</v>
@@ -26121,7 +26121,7 @@
         <v>865.0599999999999</v>
       </c>
       <c r="K578" t="n">
-        <v>2080.14</v>
+        <v>2079.05</v>
       </c>
       <c r="L578" t="b">
         <v>0</v>
@@ -26163,7 +26163,7 @@
         <v>817</v>
       </c>
       <c r="K579" t="n">
-        <v>1942.01</v>
+        <v>1940.99</v>
       </c>
       <c r="L579" t="b">
         <v>0</v>
@@ -26205,7 +26205,7 @@
         <v>768.9400000000001</v>
       </c>
       <c r="K580" t="n">
-        <v>1808.68</v>
+        <v>1807.73</v>
       </c>
       <c r="L580" t="b">
         <v>0</v>
@@ -26247,7 +26247,7 @@
         <v>720.88</v>
       </c>
       <c r="K581" t="n">
-        <v>1678.17</v>
+        <v>1677.3</v>
       </c>
       <c r="L581" t="b">
         <v>0</v>
@@ -26289,7 +26289,7 @@
         <v>672.8200000000001</v>
       </c>
       <c r="K582" t="n">
-        <v>1548.74</v>
+        <v>1547.96</v>
       </c>
       <c r="L582" t="b">
         <v>0</v>
@@ -26373,7 +26373,7 @@
         <v>576.71</v>
       </c>
       <c r="K584" t="n">
-        <v>1299.02</v>
+        <v>1298.39</v>
       </c>
       <c r="L584" t="b">
         <v>0</v>
@@ -26415,7 +26415,7 @@
         <v>528.65</v>
       </c>
       <c r="K585" t="n">
-        <v>1180.9</v>
+        <v>1180.36</v>
       </c>
       <c r="L585" t="b">
         <v>0</v>
@@ -26457,7 +26457,7 @@
         <v>480.59</v>
       </c>
       <c r="K586" t="n">
-        <v>1063.37</v>
+        <v>1062.92</v>
       </c>
       <c r="L586" t="b">
         <v>0</v>
@@ -26499,7 +26499,7 @@
         <v>432.53</v>
       </c>
       <c r="K587" t="n">
-        <v>949.4400000000001</v>
+        <v>949.04</v>
       </c>
       <c r="L587" t="b">
         <v>0</v>
@@ -26541,7 +26541,7 @@
         <v>384.47</v>
       </c>
       <c r="K588" t="n">
-        <v>836.49</v>
+        <v>836.17</v>
       </c>
       <c r="L588" t="b">
         <v>0</v>
@@ -26583,7 +26583,7 @@
         <v>336.41</v>
       </c>
       <c r="K589" t="n">
-        <v>726.0599999999999</v>
+        <v>725.78</v>
       </c>
       <c r="L589" t="b">
         <v>0</v>
@@ -26625,7 +26625,7 @@
         <v>288.35</v>
       </c>
       <c r="K590" t="n">
-        <v>617.42</v>
+        <v>617.2</v>
       </c>
       <c r="L590" t="b">
         <v>0</v>
@@ -26751,7 +26751,7 @@
         <v>144.18</v>
       </c>
       <c r="K593" t="n">
-        <v>302.75</v>
+        <v>302.66</v>
       </c>
       <c r="L593" t="b">
         <v>0</v>
@@ -26835,7 +26835,7 @@
         <v>48.06</v>
       </c>
       <c r="K595" t="n">
-        <v>99.8</v>
+        <v>99.77</v>
       </c>
       <c r="L595" t="b">
         <v>0</v>
@@ -26877,7 +26877,7 @@
         <v>777.61</v>
       </c>
       <c r="K596" t="n">
-        <v>3609.22</v>
+        <v>3608.03</v>
       </c>
       <c r="L596" t="b">
         <v>1</v>
@@ -26919,7 +26919,7 @@
         <v>777.61</v>
       </c>
       <c r="K597" t="n">
-        <v>3583.18</v>
+        <v>3582</v>
       </c>
       <c r="L597" t="b">
         <v>1</v>
@@ -26961,7 +26961,7 @@
         <v>777.61</v>
       </c>
       <c r="K598" t="n">
-        <v>3558.5</v>
+        <v>3557.23</v>
       </c>
       <c r="L598" t="b">
         <v>1</v>
@@ -27003,7 +27003,7 @@
         <v>777.61</v>
       </c>
       <c r="K599" t="n">
-        <v>3531.58</v>
+        <v>3530.23</v>
       </c>
       <c r="L599" t="b">
         <v>1</v>
@@ -27045,7 +27045,7 @@
         <v>777.61</v>
       </c>
       <c r="K600" t="n">
-        <v>3501.88</v>
+        <v>3500.54</v>
       </c>
       <c r="L600" t="b">
         <v>1</v>
@@ -27129,7 +27129,7 @@
         <v>777.61</v>
       </c>
       <c r="K602" t="n">
-        <v>3442.12</v>
+        <v>3440.74</v>
       </c>
       <c r="L602" t="b">
         <v>0</v>
@@ -27255,7 +27255,7 @@
         <v>738.73</v>
       </c>
       <c r="K605" t="n">
-        <v>3189.53</v>
+        <v>3188.25</v>
       </c>
       <c r="L605" t="b">
         <v>0</v>
@@ -27297,7 +27297,7 @@
         <v>725.77</v>
       </c>
       <c r="K606" t="n">
-        <v>3105.98</v>
+        <v>3104.73</v>
       </c>
       <c r="L606" t="b">
         <v>0</v>
@@ -27339,7 +27339,7 @@
         <v>712.8099999999999</v>
       </c>
       <c r="K607" t="n">
-        <v>3022.62</v>
+        <v>3021.35</v>
       </c>
       <c r="L607" t="b">
         <v>0</v>
@@ -27381,7 +27381,7 @@
         <v>699.85</v>
       </c>
       <c r="K608" t="n">
-        <v>2944.93</v>
+        <v>2943.65</v>
       </c>
       <c r="L608" t="b">
         <v>0</v>
@@ -27507,7 +27507,7 @@
         <v>660.97</v>
       </c>
       <c r="K611" t="n">
-        <v>2703.41</v>
+        <v>2702.18</v>
       </c>
       <c r="L611" t="b">
         <v>0</v>
@@ -27591,7 +27591,7 @@
         <v>635.05</v>
       </c>
       <c r="K613" t="n">
-        <v>2547.75</v>
+        <v>2546.56</v>
       </c>
       <c r="L613" t="b">
         <v>0</v>
@@ -27633,7 +27633,7 @@
         <v>622.09</v>
       </c>
       <c r="K614" t="n">
-        <v>2470.82</v>
+        <v>2469.72</v>
       </c>
       <c r="L614" t="b">
         <v>0</v>
@@ -27675,7 +27675,7 @@
         <v>609.13</v>
       </c>
       <c r="K615" t="n">
-        <v>2397.85</v>
+        <v>2396.78</v>
       </c>
       <c r="L615" t="b">
         <v>0</v>
@@ -27717,7 +27717,7 @@
         <v>596.17</v>
       </c>
       <c r="K616" t="n">
-        <v>2326.69</v>
+        <v>2325.69</v>
       </c>
       <c r="L616" t="b">
         <v>0</v>
@@ -27759,7 +27759,7 @@
         <v>583.21</v>
       </c>
       <c r="K617" t="n">
-        <v>2255.2</v>
+        <v>2254.28</v>
       </c>
       <c r="L617" t="b">
         <v>0</v>
@@ -27843,7 +27843,7 @@
         <v>557.29</v>
       </c>
       <c r="K619" t="n">
-        <v>2117.15</v>
+        <v>2116.32</v>
       </c>
       <c r="L619" t="b">
         <v>0</v>
@@ -27885,7 +27885,7 @@
         <v>544.33</v>
       </c>
       <c r="K620" t="n">
-        <v>2052.88</v>
+        <v>2052.13</v>
       </c>
       <c r="L620" t="b">
         <v>0</v>
@@ -27969,7 +27969,7 @@
         <v>518.41</v>
       </c>
       <c r="K622" t="n">
-        <v>1926.98</v>
+        <v>1926.33</v>
       </c>
       <c r="L622" t="b">
         <v>0</v>
@@ -28095,7 +28095,7 @@
         <v>479.53</v>
       </c>
       <c r="K625" t="n">
-        <v>1746.25</v>
+        <v>1745.72</v>
       </c>
       <c r="L625" t="b">
         <v>0</v>
@@ -28137,7 +28137,7 @@
         <v>466.57</v>
       </c>
       <c r="K626" t="n">
-        <v>1688.68</v>
+        <v>1688.2</v>
       </c>
       <c r="L626" t="b">
         <v>0</v>
@@ -28179,7 +28179,7 @@
         <v>453.6</v>
       </c>
       <c r="K627" t="n">
-        <v>1632.54</v>
+        <v>1632.09</v>
       </c>
       <c r="L627" t="b">
         <v>0</v>
@@ -28221,7 +28221,7 @@
         <v>440.64</v>
       </c>
       <c r="K628" t="n">
-        <v>1576.81</v>
+        <v>1576.37</v>
       </c>
       <c r="L628" t="b">
         <v>0</v>
@@ -28263,7 +28263,7 @@
         <v>427.68</v>
       </c>
       <c r="K629" t="n">
-        <v>1521.66</v>
+        <v>1521.25</v>
       </c>
       <c r="L629" t="b">
         <v>0</v>
@@ -28305,7 +28305,7 @@
         <v>414.72</v>
       </c>
       <c r="K630" t="n">
-        <v>1467.49</v>
+        <v>1467.09</v>
       </c>
       <c r="L630" t="b">
         <v>0</v>
@@ -28431,7 +28431,7 @@
         <v>375.84</v>
       </c>
       <c r="K633" t="n">
-        <v>1307.91</v>
+        <v>1307.55</v>
       </c>
       <c r="L633" t="b">
         <v>0</v>
@@ -28473,7 +28473,7 @@
         <v>362.88</v>
       </c>
       <c r="K634" t="n">
-        <v>1255.34</v>
+        <v>1254.99</v>
       </c>
       <c r="L634" t="b">
         <v>0</v>
@@ -28515,7 +28515,7 @@
         <v>349.92</v>
       </c>
       <c r="K635" t="n">
-        <v>1203.08</v>
+        <v>1202.72</v>
       </c>
       <c r="L635" t="b">
         <v>0</v>
@@ -28557,7 +28557,7 @@
         <v>336.96</v>
       </c>
       <c r="K636" t="n">
-        <v>1151.14</v>
+        <v>1150.78</v>
       </c>
       <c r="L636" t="b">
         <v>0</v>
@@ -28599,7 +28599,7 @@
         <v>324</v>
       </c>
       <c r="K637" t="n">
-        <v>1098.75</v>
+        <v>1098.4</v>
       </c>
       <c r="L637" t="b">
         <v>0</v>
@@ -28683,7 +28683,7 @@
         <v>298.08</v>
       </c>
       <c r="K639" t="n">
-        <v>996.34</v>
+        <v>995.99</v>
       </c>
       <c r="L639" t="b">
         <v>0</v>
@@ -28809,7 +28809,7 @@
         <v>259.2</v>
       </c>
       <c r="K642" t="n">
-        <v>846.64</v>
+        <v>846.3</v>
       </c>
       <c r="L642" t="b">
         <v>0</v>
@@ -28851,7 +28851,7 @@
         <v>246.24</v>
       </c>
       <c r="K643" t="n">
-        <v>797.39</v>
+        <v>797.0700000000001</v>
       </c>
       <c r="L643" t="b">
         <v>0</v>
@@ -28893,7 +28893,7 @@
         <v>233.28</v>
       </c>
       <c r="K644" t="n">
-        <v>750.03</v>
+        <v>749.73</v>
       </c>
       <c r="L644" t="b">
         <v>0</v>
@@ -28935,7 +28935,7 @@
         <v>220.32</v>
       </c>
       <c r="K645" t="n">
-        <v>702.08</v>
+        <v>701.79</v>
       </c>
       <c r="L645" t="b">
         <v>0</v>
@@ -28977,7 +28977,7 @@
         <v>207.36</v>
       </c>
       <c r="K646" t="n">
-        <v>655.64</v>
+        <v>655.37</v>
       </c>
       <c r="L646" t="b">
         <v>0</v>
@@ -29061,7 +29061,7 @@
         <v>181.44</v>
       </c>
       <c r="K648" t="n">
-        <v>563.88</v>
+        <v>563.65</v>
       </c>
       <c r="L648" t="b">
         <v>0</v>
@@ -29145,7 +29145,7 @@
         <v>155.52</v>
       </c>
       <c r="K650" t="n">
-        <v>474.67</v>
+        <v>474.48</v>
       </c>
       <c r="L650" t="b">
         <v>0</v>
@@ -29187,7 +29187,7 @@
         <v>142.56</v>
       </c>
       <c r="K651" t="n">
-        <v>431.21</v>
+        <v>431.03</v>
       </c>
       <c r="L651" t="b">
         <v>0</v>
@@ -29229,7 +29229,7 @@
         <v>129.6</v>
       </c>
       <c r="K652" t="n">
-        <v>388.44</v>
+        <v>388.28</v>
       </c>
       <c r="L652" t="b">
         <v>0</v>
@@ -29271,7 +29271,7 @@
         <v>116.64</v>
       </c>
       <c r="K653" t="n">
-        <v>346.48</v>
+        <v>346.33</v>
       </c>
       <c r="L653" t="b">
         <v>0</v>
@@ -29313,7 +29313,7 @@
         <v>103.68</v>
       </c>
       <c r="K654" t="n">
-        <v>305.17</v>
+        <v>305.03</v>
       </c>
       <c r="L654" t="b">
         <v>0</v>
@@ -29355,7 +29355,7 @@
         <v>90.72</v>
       </c>
       <c r="K655" t="n">
-        <v>264.5</v>
+        <v>264.38</v>
       </c>
       <c r="L655" t="b">
         <v>0</v>
@@ -29439,7 +29439,7 @@
         <v>64.8</v>
       </c>
       <c r="K657" t="n">
-        <v>185.43</v>
+        <v>185.34</v>
       </c>
       <c r="L657" t="b">
         <v>0</v>
@@ -29523,7 +29523,7 @@
         <v>38.88</v>
       </c>
       <c r="K659" t="n">
-        <v>109.1</v>
+        <v>109.04</v>
       </c>
       <c r="L659" t="b">
         <v>0</v>
@@ -29565,7 +29565,7 @@
         <v>25.92</v>
       </c>
       <c r="K660" t="n">
-        <v>71.92</v>
+        <v>71.89</v>
       </c>
       <c r="L660" t="b">
         <v>0</v>
@@ -29607,7 +29607,7 @@
         <v>12.96</v>
       </c>
       <c r="K661" t="n">
-        <v>35.56</v>
+        <v>35.54</v>
       </c>
       <c r="L661" t="b">
         <v>0</v>
@@ -29649,7 +29649,7 @@
         <v>653.21</v>
       </c>
       <c r="K662" t="n">
-        <v>3009.97</v>
+        <v>3008.98</v>
       </c>
       <c r="L662" t="b">
         <v>1</v>
@@ -29691,7 +29691,7 @@
         <v>653.21</v>
       </c>
       <c r="K663" t="n">
-        <v>2989.24</v>
+        <v>2988.17</v>
       </c>
       <c r="L663" t="b">
         <v>1</v>
@@ -29733,7 +29733,7 @@
         <v>653.21</v>
       </c>
       <c r="K664" t="n">
-        <v>2966.63</v>
+        <v>2965.49</v>
       </c>
       <c r="L664" t="b">
         <v>1</v>
@@ -29775,7 +29775,7 @@
         <v>653.21</v>
       </c>
       <c r="K665" t="n">
-        <v>2941.68</v>
+        <v>2940.55</v>
       </c>
       <c r="L665" t="b">
         <v>0</v>
@@ -29859,7 +29859,7 @@
         <v>626</v>
       </c>
       <c r="K667" t="n">
-        <v>2771</v>
+        <v>2769.89</v>
       </c>
       <c r="L667" t="b">
         <v>0</v>
@@ -29985,7 +29985,7 @@
         <v>585.17</v>
       </c>
       <c r="K670" t="n">
-        <v>2526.53</v>
+        <v>2525.51</v>
       </c>
       <c r="L670" t="b">
         <v>0</v>
@@ -30027,7 +30027,7 @@
         <v>571.5599999999999</v>
       </c>
       <c r="K671" t="n">
-        <v>2446.04</v>
+        <v>2445.06</v>
       </c>
       <c r="L671" t="b">
         <v>0</v>
@@ -30069,7 +30069,7 @@
         <v>557.95</v>
       </c>
       <c r="K672" t="n">
-        <v>2365.97</v>
+        <v>2364.97</v>
       </c>
       <c r="L672" t="b">
         <v>0</v>
@@ -30111,7 +30111,7 @@
         <v>544.34</v>
       </c>
       <c r="K673" t="n">
-        <v>2290.58</v>
+        <v>2289.58</v>
       </c>
       <c r="L673" t="b">
         <v>0</v>
@@ -30237,7 +30237,7 @@
         <v>503.52</v>
       </c>
       <c r="K676" t="n">
-        <v>2059.43</v>
+        <v>2058.49</v>
       </c>
       <c r="L676" t="b">
         <v>0</v>
@@ -30321,7 +30321,7 @@
         <v>476.3</v>
       </c>
       <c r="K678" t="n">
-        <v>1910.87</v>
+        <v>1909.98</v>
       </c>
       <c r="L678" t="b">
         <v>0</v>
@@ -30363,7 +30363,7 @@
         <v>462.69</v>
       </c>
       <c r="K679" t="n">
-        <v>1837.74</v>
+        <v>1836.91</v>
       </c>
       <c r="L679" t="b">
         <v>0</v>
@@ -30405,7 +30405,7 @@
         <v>449.08</v>
       </c>
       <c r="K680" t="n">
-        <v>1767.84</v>
+        <v>1767.05</v>
       </c>
       <c r="L680" t="b">
         <v>0</v>
@@ -30447,7 +30447,7 @@
         <v>435.48</v>
       </c>
       <c r="K681" t="n">
-        <v>1699.55</v>
+        <v>1698.82</v>
       </c>
       <c r="L681" t="b">
         <v>0</v>
@@ -30489,7 +30489,7 @@
         <v>421.87</v>
       </c>
       <c r="K682" t="n">
-        <v>1631.32</v>
+        <v>1630.65</v>
       </c>
       <c r="L682" t="b">
         <v>0</v>
@@ -30573,7 +30573,7 @@
         <v>394.65</v>
       </c>
       <c r="K684" t="n">
-        <v>1499.29</v>
+        <v>1498.7</v>
       </c>
       <c r="L684" t="b">
         <v>0</v>
@@ -30615,7 +30615,7 @@
         <v>381.04</v>
       </c>
       <c r="K685" t="n">
-        <v>1437.06</v>
+        <v>1436.54</v>
       </c>
       <c r="L685" t="b">
         <v>0</v>
@@ -30699,7 +30699,7 @@
         <v>353.82</v>
       </c>
       <c r="K687" t="n">
-        <v>1315.21</v>
+        <v>1314.77</v>
       </c>
       <c r="L687" t="b">
         <v>0</v>
@@ -30825,7 +30825,7 @@
         <v>313</v>
       </c>
       <c r="K690" t="n">
-        <v>1139.82</v>
+        <v>1139.48</v>
       </c>
       <c r="L690" t="b">
         <v>0</v>
@@ -30867,7 +30867,7 @@
         <v>299.39</v>
       </c>
       <c r="K691" t="n">
-        <v>1083.6</v>
+        <v>1083.3</v>
       </c>
       <c r="L691" t="b">
         <v>0</v>
@@ -30909,7 +30909,7 @@
         <v>285.78</v>
       </c>
       <c r="K692" t="n">
-        <v>1028.53</v>
+        <v>1028.25</v>
       </c>
       <c r="L692" t="b">
         <v>0</v>
@@ -30951,7 +30951,7 @@
         <v>272.17</v>
       </c>
       <c r="K693" t="n">
-        <v>973.9400000000001</v>
+        <v>973.6799999999999</v>
       </c>
       <c r="L693" t="b">
         <v>0</v>
@@ -30993,7 +30993,7 @@
         <v>258.56</v>
       </c>
       <c r="K694" t="n">
-        <v>919.9400000000001</v>
+        <v>919.6900000000001</v>
       </c>
       <c r="L694" t="b">
         <v>0</v>
@@ -31035,7 +31035,7 @@
         <v>244.95</v>
       </c>
       <c r="K695" t="n">
-        <v>866.77</v>
+        <v>866.53</v>
       </c>
       <c r="L695" t="b">
         <v>0</v>
@@ -31161,7 +31161,7 @@
         <v>204.13</v>
       </c>
       <c r="K698" t="n">
-        <v>710.35</v>
+        <v>710.16</v>
       </c>
       <c r="L698" t="b">
         <v>0</v>
@@ -31203,7 +31203,7 @@
         <v>190.52</v>
       </c>
       <c r="K699" t="n">
-        <v>659.08</v>
+        <v>658.89</v>
       </c>
       <c r="L699" t="b">
         <v>0</v>
@@ -31245,7 +31245,7 @@
         <v>176.91</v>
       </c>
       <c r="K700" t="n">
-        <v>608.25</v>
+        <v>608.0599999999999</v>
       </c>
       <c r="L700" t="b">
         <v>0</v>
@@ -31287,7 +31287,7 @@
         <v>163.3</v>
       </c>
       <c r="K701" t="n">
-        <v>557.88</v>
+        <v>557.7</v>
       </c>
       <c r="L701" t="b">
         <v>0</v>
@@ -31329,7 +31329,7 @@
         <v>149.69</v>
       </c>
       <c r="K702" t="n">
-        <v>507.64</v>
+        <v>507.48</v>
       </c>
       <c r="L702" t="b">
         <v>0</v>
@@ -31413,7 +31413,7 @@
         <v>122.48</v>
       </c>
       <c r="K704" t="n">
-        <v>409.38</v>
+        <v>409.23</v>
       </c>
       <c r="L704" t="b">
         <v>0</v>
@@ -31539,7 +31539,7 @@
         <v>81.65000000000001</v>
       </c>
       <c r="K707" t="n">
-        <v>266.7</v>
+        <v>266.59</v>
       </c>
       <c r="L707" t="b">
         <v>0</v>
@@ -31581,7 +31581,7 @@
         <v>68.04000000000001</v>
       </c>
       <c r="K708" t="n">
-        <v>220.34</v>
+        <v>220.25</v>
       </c>
       <c r="L708" t="b">
         <v>0</v>
@@ -31623,7 +31623,7 @@
         <v>54.43</v>
       </c>
       <c r="K709" t="n">
-        <v>175.01</v>
+        <v>174.94</v>
       </c>
       <c r="L709" t="b">
         <v>0</v>
@@ -31665,7 +31665,7 @@
         <v>40.83</v>
       </c>
       <c r="K710" t="n">
-        <v>130.09</v>
+        <v>130.04</v>
       </c>
       <c r="L710" t="b">
         <v>0</v>
@@ -31707,7 +31707,7 @@
         <v>27.22</v>
       </c>
       <c r="K711" t="n">
-        <v>86.06</v>
+        <v>86.02</v>
       </c>
       <c r="L711" t="b">
         <v>0</v>
@@ -31791,7 +31791,7 @@
         <v>2000.21</v>
       </c>
       <c r="K713" t="n">
-        <v>9153.4</v>
+        <v>9150.129999999999</v>
       </c>
       <c r="L713" t="b">
         <v>1</v>
@@ -31833,7 +31833,7 @@
         <v>2000.21</v>
       </c>
       <c r="K714" t="n">
-        <v>9084.15</v>
+        <v>9080.66</v>
       </c>
       <c r="L714" t="b">
         <v>1</v>
@@ -31875,7 +31875,7 @@
         <v>2000.21</v>
       </c>
       <c r="K715" t="n">
-        <v>9007.76</v>
+        <v>9004.299999999999</v>
       </c>
       <c r="L715" t="b">
         <v>1</v>
@@ -31959,7 +31959,7 @@
         <v>2000.21</v>
       </c>
       <c r="K717" t="n">
-        <v>8854.040000000001</v>
+        <v>8850.48</v>
       </c>
       <c r="L717" t="b">
         <v>1</v>
@@ -32085,7 +32085,7 @@
         <v>1972.43</v>
       </c>
       <c r="K720" t="n">
-        <v>8516.17</v>
+        <v>8512.75</v>
       </c>
       <c r="L720" t="b">
         <v>0</v>
@@ -32127,7 +32127,7 @@
         <v>1944.65</v>
       </c>
       <c r="K721" t="n">
-        <v>8322.290000000001</v>
+        <v>8318.940000000001</v>
       </c>
       <c r="L721" t="b">
         <v>0</v>
@@ -32169,7 +32169,7 @@
         <v>1916.87</v>
       </c>
       <c r="K722" t="n">
-        <v>8128.37</v>
+        <v>8124.96</v>
       </c>
       <c r="L722" t="b">
         <v>0</v>
@@ -32211,7 +32211,7 @@
         <v>1889.09</v>
       </c>
       <c r="K723" t="n">
-        <v>7949.22</v>
+        <v>7945.74</v>
       </c>
       <c r="L723" t="b">
         <v>0</v>
@@ -32337,7 +32337,7 @@
         <v>1805.75</v>
       </c>
       <c r="K726" t="n">
-        <v>7385.66</v>
+        <v>7382.29</v>
       </c>
       <c r="L726" t="b">
         <v>0</v>
@@ -32421,7 +32421,7 @@
         <v>1750.19</v>
       </c>
       <c r="K728" t="n">
-        <v>7021.57</v>
+        <v>7018.31</v>
       </c>
       <c r="L728" t="b">
         <v>0</v>
@@ -32463,7 +32463,7 @@
         <v>1722.4</v>
       </c>
       <c r="K729" t="n">
-        <v>6841.1</v>
+        <v>6838.05</v>
       </c>
       <c r="L729" t="b">
         <v>0</v>
@@ -32505,7 +32505,7 @@
         <v>1694.62</v>
       </c>
       <c r="K730" t="n">
-        <v>6670.96</v>
+        <v>6667.99</v>
       </c>
       <c r="L730" t="b">
         <v>0</v>
@@ -32547,7 +32547,7 @@
         <v>1666.84</v>
       </c>
       <c r="K731" t="n">
-        <v>6505.28</v>
+        <v>6502.49</v>
       </c>
       <c r="L731" t="b">
         <v>0</v>
@@ -32589,7 +32589,7 @@
         <v>1639.06</v>
       </c>
       <c r="K732" t="n">
-        <v>6338.1</v>
+        <v>6335.49</v>
       </c>
       <c r="L732" t="b">
         <v>0</v>
@@ -32673,7 +32673,7 @@
         <v>1583.5</v>
       </c>
       <c r="K734" t="n">
-        <v>6015.78</v>
+        <v>6013.42</v>
       </c>
       <c r="L734" t="b">
         <v>0</v>
@@ -32715,7 +32715,7 @@
         <v>1555.72</v>
       </c>
       <c r="K735" t="n">
-        <v>5867.27</v>
+        <v>5865.12</v>
       </c>
       <c r="L735" t="b">
         <v>0</v>
@@ -32799,7 +32799,7 @@
         <v>1500.16</v>
       </c>
       <c r="K737" t="n">
-        <v>5576.29</v>
+        <v>5574.41</v>
       </c>
       <c r="L737" t="b">
         <v>0</v>
@@ -32925,7 +32925,7 @@
         <v>1416.82</v>
       </c>
       <c r="K740" t="n">
-        <v>5159.52</v>
+        <v>5157.96</v>
       </c>
       <c r="L740" t="b">
         <v>0</v>
@@ -32967,7 +32967,7 @@
         <v>1389.04</v>
       </c>
       <c r="K741" t="n">
-        <v>5027.46</v>
+        <v>5026.04</v>
       </c>
       <c r="L741" t="b">
         <v>0</v>
@@ -33009,7 +33009,7 @@
         <v>1361.26</v>
       </c>
       <c r="K742" t="n">
-        <v>4899.2</v>
+        <v>4897.86</v>
       </c>
       <c r="L742" t="b">
         <v>0</v>
@@ -33051,7 +33051,7 @@
         <v>1333.47</v>
       </c>
       <c r="K743" t="n">
-        <v>4771.71</v>
+        <v>4770.41</v>
       </c>
       <c r="L743" t="b">
         <v>0</v>
@@ -33093,7 +33093,7 @@
         <v>1305.69</v>
       </c>
       <c r="K744" t="n">
-        <v>4645.54</v>
+        <v>4644.27</v>
       </c>
       <c r="L744" t="b">
         <v>0</v>
@@ -33135,7 +33135,7 @@
         <v>1277.91</v>
       </c>
       <c r="K745" t="n">
-        <v>4521.86</v>
+        <v>4520.63</v>
       </c>
       <c r="L745" t="b">
         <v>0</v>
@@ -33261,7 +33261,7 @@
         <v>1194.57</v>
       </c>
       <c r="K748" t="n">
-        <v>4157.02</v>
+        <v>4155.88</v>
       </c>
       <c r="L748" t="b">
         <v>0</v>
@@ -33303,7 +33303,7 @@
         <v>1166.79</v>
       </c>
       <c r="K749" t="n">
-        <v>4036.33</v>
+        <v>4035.19</v>
       </c>
       <c r="L749" t="b">
         <v>0</v>
@@ -33345,7 +33345,7 @@
         <v>1139.01</v>
       </c>
       <c r="K750" t="n">
-        <v>3916.06</v>
+        <v>3914.88</v>
       </c>
       <c r="L750" t="b">
         <v>0</v>
@@ -33387,7 +33387,7 @@
         <v>1111.23</v>
       </c>
       <c r="K751" t="n">
-        <v>3796.21</v>
+        <v>3794.99</v>
       </c>
       <c r="L751" t="b">
         <v>0</v>
@@ -33429,7 +33429,7 @@
         <v>1083.45</v>
       </c>
       <c r="K752" t="n">
-        <v>3674.15</v>
+        <v>3672.98</v>
       </c>
       <c r="L752" t="b">
         <v>0</v>
@@ -33513,7 +33513,7 @@
         <v>1027.89</v>
       </c>
       <c r="K754" t="n">
-        <v>3435.71</v>
+        <v>3434.48</v>
       </c>
       <c r="L754" t="b">
         <v>0</v>
@@ -33639,7 +33639,7 @@
         <v>944.54</v>
       </c>
       <c r="K757" t="n">
-        <v>3085.17</v>
+        <v>3083.96</v>
       </c>
       <c r="L757" t="b">
         <v>0</v>
@@ -33681,7 +33681,7 @@
         <v>916.76</v>
       </c>
       <c r="K758" t="n">
-        <v>2968.68</v>
+        <v>2967.52</v>
       </c>
       <c r="L758" t="b">
         <v>0</v>
@@ -33723,7 +33723,7 @@
         <v>888.98</v>
       </c>
       <c r="K759" t="n">
-        <v>2858.19</v>
+        <v>2857.04</v>
       </c>
       <c r="L759" t="b">
         <v>0</v>
@@ -33765,7 +33765,7 @@
         <v>861.2</v>
       </c>
       <c r="K760" t="n">
-        <v>2744.3</v>
+        <v>2743.17</v>
       </c>
       <c r="L760" t="b">
         <v>0</v>
@@ -33807,7 +33807,7 @@
         <v>833.42</v>
       </c>
       <c r="K761" t="n">
-        <v>2635.14</v>
+        <v>2634.05</v>
       </c>
       <c r="L761" t="b">
         <v>0</v>
@@ -33891,7 +33891,7 @@
         <v>777.86</v>
       </c>
       <c r="K763" t="n">
-        <v>2417.41</v>
+        <v>2416.42</v>
       </c>
       <c r="L763" t="b">
         <v>0</v>
@@ -33975,7 +33975,7 @@
         <v>722.3</v>
       </c>
       <c r="K765" t="n">
-        <v>2204.55</v>
+        <v>2203.65</v>
       </c>
       <c r="L765" t="b">
         <v>0</v>
@@ -34017,7 +34017,7 @@
         <v>694.52</v>
       </c>
       <c r="K766" t="n">
-        <v>2100.7</v>
+        <v>2099.84</v>
       </c>
       <c r="L766" t="b">
         <v>0</v>
@@ -34059,7 +34059,7 @@
         <v>666.74</v>
       </c>
       <c r="K767" t="n">
-        <v>1998.33</v>
+        <v>1997.49</v>
       </c>
       <c r="L767" t="b">
         <v>0</v>
@@ -34101,7 +34101,7 @@
         <v>638.96</v>
       </c>
       <c r="K768" t="n">
-        <v>1898</v>
+        <v>1897.17</v>
       </c>
       <c r="L768" t="b">
         <v>0</v>
@@ -34143,7 +34143,7 @@
         <v>611.1799999999999</v>
       </c>
       <c r="K769" t="n">
-        <v>1798.88</v>
+        <v>1798.1</v>
       </c>
       <c r="L769" t="b">
         <v>0</v>
@@ -34185,7 +34185,7 @@
         <v>583.4</v>
       </c>
       <c r="K770" t="n">
-        <v>1700.91</v>
+        <v>1700.13</v>
       </c>
       <c r="L770" t="b">
         <v>0</v>
@@ -34269,7 +34269,7 @@
         <v>527.83</v>
       </c>
       <c r="K772" t="n">
-        <v>1510.38</v>
+        <v>1509.67</v>
       </c>
       <c r="L772" t="b">
         <v>0</v>
@@ -34353,7 +34353,7 @@
         <v>472.27</v>
       </c>
       <c r="K774" t="n">
-        <v>1325.2</v>
+        <v>1324.53</v>
       </c>
       <c r="L774" t="b">
         <v>0</v>
@@ -34395,7 +34395,7 @@
         <v>444.49</v>
       </c>
       <c r="K775" t="n">
-        <v>1233.39</v>
+        <v>1232.77</v>
       </c>
       <c r="L775" t="b">
         <v>0</v>
@@ -34437,7 +34437,7 @@
         <v>416.71</v>
       </c>
       <c r="K776" t="n">
-        <v>1143.22</v>
+        <v>1142.62</v>
       </c>
       <c r="L776" t="b">
         <v>0</v>
@@ -34479,7 +34479,7 @@
         <v>388.93</v>
       </c>
       <c r="K777" t="n">
-        <v>1055.3</v>
+        <v>1054.75</v>
       </c>
       <c r="L777" t="b">
         <v>0</v>
@@ -34521,7 +34521,7 @@
         <v>361.15</v>
       </c>
       <c r="K778" t="n">
-        <v>969.1799999999999</v>
+        <v>968.67</v>
       </c>
       <c r="L778" t="b">
         <v>0</v>
@@ -34605,7 +34605,7 @@
         <v>305.59</v>
       </c>
       <c r="K780" t="n">
-        <v>802.1799999999999</v>
+        <v>801.76</v>
       </c>
       <c r="L780" t="b">
         <v>0</v>
@@ -34689,7 +34689,7 @@
         <v>250.03</v>
       </c>
       <c r="K782" t="n">
-        <v>642.6900000000001</v>
+        <v>642.35</v>
       </c>
       <c r="L782" t="b">
         <v>0</v>
@@ -34731,7 +34731,7 @@
         <v>222.25</v>
       </c>
       <c r="K783" t="n">
-        <v>565.01</v>
+        <v>564.71</v>
       </c>
       <c r="L783" t="b">
         <v>0</v>
@@ -34857,7 +34857,7 @@
         <v>138.9</v>
       </c>
       <c r="K786" t="n">
-        <v>341.64</v>
+        <v>341.46</v>
       </c>
       <c r="L786" t="b">
         <v>0</v>
@@ -34941,7 +34941,7 @@
         <v>83.34</v>
       </c>
       <c r="K788" t="n">
-        <v>200.41</v>
+        <v>200.3</v>
       </c>
       <c r="L788" t="b">
         <v>0</v>
@@ -34983,7 +34983,7 @@
         <v>55.56</v>
       </c>
       <c r="K789" t="n">
-        <v>132.07</v>
+        <v>132</v>
       </c>
       <c r="L789" t="b">
         <v>0</v>
@@ -35025,7 +35025,7 @@
         <v>27.78</v>
       </c>
       <c r="K790" t="n">
-        <v>65.34</v>
+        <v>65.31</v>
       </c>
       <c r="L790" t="b">
         <v>0</v>
@@ -35067,7 +35067,7 @@
         <v>341.61</v>
       </c>
       <c r="K791" t="n">
-        <v>1551.45</v>
+        <v>1550.85</v>
       </c>
       <c r="L791" t="b">
         <v>0</v>
@@ -35109,7 +35109,7 @@
         <v>332.12</v>
       </c>
       <c r="K792" t="n">
-        <v>1495.67</v>
+        <v>1495.09</v>
       </c>
       <c r="L792" t="b">
         <v>0</v>
@@ -35193,7 +35193,7 @@
         <v>313.14</v>
       </c>
       <c r="K794" t="n">
-        <v>1386.14</v>
+        <v>1385.58</v>
       </c>
       <c r="L794" t="b">
         <v>0</v>
@@ -35319,7 +35319,7 @@
         <v>284.67</v>
       </c>
       <c r="K797" t="n">
-        <v>1229.11</v>
+        <v>1228.61</v>
       </c>
       <c r="L797" t="b">
         <v>0</v>
@@ -35361,7 +35361,7 @@
         <v>275.18</v>
       </c>
       <c r="K798" t="n">
-        <v>1177.68</v>
+        <v>1177.2</v>
       </c>
       <c r="L798" t="b">
         <v>0</v>
@@ -35403,7 +35403,7 @@
         <v>265.7</v>
       </c>
       <c r="K799" t="n">
-        <v>1126.67</v>
+        <v>1126.19</v>
       </c>
       <c r="L799" t="b">
         <v>0</v>
@@ -35445,7 +35445,7 @@
         <v>256.21</v>
       </c>
       <c r="K800" t="n">
-        <v>1078.11</v>
+        <v>1077.64</v>
       </c>
       <c r="L800" t="b">
         <v>0</v>
@@ -35571,7 +35571,7 @@
         <v>227.74</v>
       </c>
       <c r="K803" t="n">
-        <v>931.47</v>
+        <v>931.05</v>
       </c>
       <c r="L803" t="b">
         <v>0</v>
@@ -35655,7 +35655,7 @@
         <v>208.76</v>
       </c>
       <c r="K805" t="n">
-        <v>837.53</v>
+        <v>837.14</v>
       </c>
       <c r="L805" t="b">
         <v>0</v>
@@ -35697,7 +35697,7 @@
         <v>199.27</v>
       </c>
       <c r="K806" t="n">
-        <v>791.47</v>
+        <v>791.12</v>
       </c>
       <c r="L806" t="b">
         <v>0</v>
@@ -35739,7 +35739,7 @@
         <v>189.78</v>
       </c>
       <c r="K807" t="n">
-        <v>747.09</v>
+        <v>746.75</v>
       </c>
       <c r="L807" t="b">
         <v>0</v>
@@ -35781,7 +35781,7 @@
         <v>180.29</v>
       </c>
       <c r="K808" t="n">
-        <v>703.64</v>
+        <v>703.34</v>
       </c>
       <c r="L808" t="b">
         <v>0</v>
@@ -35823,7 +35823,7 @@
         <v>170.8</v>
       </c>
       <c r="K809" t="n">
-        <v>660.48</v>
+        <v>660.21</v>
       </c>
       <c r="L809" t="b">
         <v>0</v>
@@ -35907,7 +35907,7 @@
         <v>151.83</v>
       </c>
       <c r="K811" t="n">
-        <v>576.79</v>
+        <v>576.5700000000001</v>
       </c>
       <c r="L811" t="b">
         <v>0</v>
@@ -35949,7 +35949,7 @@
         <v>142.34</v>
       </c>
       <c r="K812" t="n">
-        <v>536.8099999999999</v>
+        <v>536.62</v>
       </c>
       <c r="L812" t="b">
         <v>0</v>
@@ -36033,7 +36033,7 @@
         <v>123.36</v>
       </c>
       <c r="K814" t="n">
-        <v>458.54</v>
+        <v>458.39</v>
       </c>
       <c r="L814" t="b">
         <v>0</v>
@@ -36159,7 +36159,7 @@
         <v>94.89</v>
       </c>
       <c r="K817" t="n">
-        <v>345.56</v>
+        <v>345.45</v>
       </c>
       <c r="L817" t="b">
         <v>0</v>
@@ -36201,7 +36201,7 @@
         <v>85.40000000000001</v>
       </c>
       <c r="K818" t="n">
-        <v>309.1</v>
+        <v>309.02</v>
       </c>
       <c r="L818" t="b">
         <v>0</v>
@@ -36243,7 +36243,7 @@
         <v>75.91</v>
       </c>
       <c r="K819" t="n">
-        <v>273.21</v>
+        <v>273.14</v>
       </c>
       <c r="L819" t="b">
         <v>0</v>
@@ -36285,7 +36285,7 @@
         <v>66.42</v>
       </c>
       <c r="K820" t="n">
-        <v>237.69</v>
+        <v>237.63</v>
       </c>
       <c r="L820" t="b">
         <v>0</v>
@@ -36327,7 +36327,7 @@
         <v>56.93</v>
       </c>
       <c r="K821" t="n">
-        <v>202.57</v>
+        <v>202.51</v>
       </c>
       <c r="L821" t="b">
         <v>0</v>
@@ -36369,7 +36369,7 @@
         <v>47.45</v>
       </c>
       <c r="K822" t="n">
-        <v>167.89</v>
+        <v>167.84</v>
       </c>
       <c r="L822" t="b">
         <v>0</v>
@@ -36495,7 +36495,7 @@
         <v>18.98</v>
       </c>
       <c r="K825" t="n">
-        <v>66.04000000000001</v>
+        <v>66.02</v>
       </c>
       <c r="L825" t="b">
         <v>0</v>
@@ -36537,7 +36537,7 @@
         <v>9.49</v>
       </c>
       <c r="K826" t="n">
-        <v>32.83</v>
+        <v>32.82</v>
       </c>
       <c r="L826" t="b">
         <v>0</v>
@@ -36621,7 +36621,7 @@
         <v>2608.76</v>
       </c>
       <c r="K828" t="n">
-        <v>11547.79</v>
+        <v>11543.15</v>
       </c>
       <c r="L828" t="b">
         <v>1</v>
@@ -36747,7 +36747,7 @@
         <v>2608.76</v>
       </c>
       <c r="K831" t="n">
-        <v>11263.57</v>
+        <v>11259.04</v>
       </c>
       <c r="L831" t="b">
         <v>1</v>
@@ -36789,7 +36789,7 @@
         <v>2608.76</v>
       </c>
       <c r="K832" t="n">
-        <v>11164.38</v>
+        <v>11159.9</v>
       </c>
       <c r="L832" t="b">
         <v>1</v>
@@ -36831,7 +36831,7 @@
         <v>2608.76</v>
       </c>
       <c r="K833" t="n">
-        <v>11062.28</v>
+        <v>11057.63</v>
       </c>
       <c r="L833" t="b">
         <v>1</v>
@@ -36873,7 +36873,7 @@
         <v>2608.76</v>
       </c>
       <c r="K834" t="n">
-        <v>10977.56</v>
+        <v>10972.75</v>
       </c>
       <c r="L834" t="b">
         <v>1</v>
@@ -36999,7 +36999,7 @@
         <v>2608.76</v>
       </c>
       <c r="K837" t="n">
-        <v>10670.03</v>
+        <v>10665.17</v>
       </c>
       <c r="L837" t="b">
         <v>1</v>
@@ -37083,7 +37083,7 @@
         <v>2608.76</v>
       </c>
       <c r="K839" t="n">
-        <v>10466.07</v>
+        <v>10461.21</v>
       </c>
       <c r="L839" t="b">
         <v>0</v>
@@ -37125,7 +37125,7 @@
         <v>2565.28</v>
       </c>
       <c r="K840" t="n">
-        <v>10188.85</v>
+        <v>10184.3</v>
       </c>
       <c r="L840" t="b">
         <v>0</v>
@@ -37167,7 +37167,7 @@
         <v>2521.8</v>
       </c>
       <c r="K841" t="n">
-        <v>9927.17</v>
+        <v>9922.74</v>
       </c>
       <c r="L841" t="b">
         <v>0</v>
@@ -37209,7 +37209,7 @@
         <v>2478.32</v>
       </c>
       <c r="K842" t="n">
-        <v>9672.27</v>
+        <v>9668.120000000001</v>
       </c>
       <c r="L842" t="b">
         <v>0</v>
@@ -37251,7 +37251,7 @@
         <v>2434.84</v>
       </c>
       <c r="K843" t="n">
-        <v>9415.290000000001</v>
+        <v>9411.42</v>
       </c>
       <c r="L843" t="b">
         <v>0</v>
@@ -37335,7 +37335,7 @@
         <v>2347.88</v>
       </c>
       <c r="K845" t="n">
-        <v>8919.690000000001</v>
+        <v>8916.190000000001</v>
       </c>
       <c r="L845" t="b">
         <v>0</v>
@@ -37377,7 +37377,7 @@
         <v>2304.4</v>
       </c>
       <c r="K846" t="n">
-        <v>8690.860000000001</v>
+        <v>8687.68</v>
       </c>
       <c r="L846" t="b">
         <v>0</v>
@@ -37461,7 +37461,7 @@
         <v>2217.44</v>
       </c>
       <c r="K848" t="n">
-        <v>8242.530000000001</v>
+        <v>8239.75</v>
       </c>
       <c r="L848" t="b">
         <v>0</v>
@@ -37587,7 +37587,7 @@
         <v>2087</v>
       </c>
       <c r="K851" t="n">
-        <v>7600.09</v>
+        <v>7597.8</v>
       </c>
       <c r="L851" t="b">
         <v>0</v>
@@ -37629,7 +37629,7 @@
         <v>2043.53</v>
       </c>
       <c r="K852" t="n">
-        <v>7396.31</v>
+        <v>7394.22</v>
       </c>
       <c r="L852" t="b">
         <v>0</v>
@@ -37671,7 +37671,7 @@
         <v>2000.05</v>
       </c>
       <c r="K853" t="n">
-        <v>7198.23</v>
+        <v>7196.26</v>
       </c>
       <c r="L853" t="b">
         <v>0</v>
@@ -37713,7 +37713,7 @@
         <v>1956.57</v>
       </c>
       <c r="K854" t="n">
-        <v>7001.39</v>
+        <v>6999.47</v>
       </c>
       <c r="L854" t="b">
         <v>0</v>
@@ -37755,7 +37755,7 @@
         <v>1913.09</v>
       </c>
       <c r="K855" t="n">
-        <v>6806.59</v>
+        <v>6804.73</v>
       </c>
       <c r="L855" t="b">
         <v>0</v>
@@ -37797,7 +37797,7 @@
         <v>1869.61</v>
       </c>
       <c r="K856" t="n">
-        <v>6615.56</v>
+        <v>6613.75</v>
       </c>
       <c r="L856" t="b">
         <v>0</v>
@@ -37923,7 +37923,7 @@
         <v>1739.17</v>
       </c>
       <c r="K859" t="n">
-        <v>6052.19</v>
+        <v>6050.53</v>
       </c>
       <c r="L859" t="b">
         <v>0</v>
@@ -37965,7 +37965,7 @@
         <v>1695.69</v>
       </c>
       <c r="K860" t="n">
-        <v>5865.98</v>
+        <v>5864.32</v>
       </c>
       <c r="L860" t="b">
         <v>0</v>
@@ -38007,7 +38007,7 @@
         <v>1652.21</v>
       </c>
       <c r="K861" t="n">
-        <v>5680.52</v>
+        <v>5678.8</v>
       </c>
       <c r="L861" t="b">
         <v>0</v>
@@ -38049,7 +38049,7 @@
         <v>1608.73</v>
       </c>
       <c r="K862" t="n">
-        <v>5495.79</v>
+        <v>5494.03</v>
       </c>
       <c r="L862" t="b">
         <v>0</v>
@@ -38091,7 +38091,7 @@
         <v>1565.25</v>
       </c>
       <c r="K863" t="n">
-        <v>5308.04</v>
+        <v>5306.34</v>
       </c>
       <c r="L863" t="b">
         <v>0</v>
@@ -38175,7 +38175,7 @@
         <v>1478.3</v>
       </c>
       <c r="K865" t="n">
-        <v>4941.2</v>
+        <v>4939.43</v>
       </c>
       <c r="L865" t="b">
         <v>0</v>
@@ -38301,7 +38301,7 @@
         <v>1347.86</v>
       </c>
       <c r="K868" t="n">
-        <v>4402.52</v>
+        <v>4400.79</v>
       </c>
       <c r="L868" t="b">
         <v>0</v>
@@ -38343,7 +38343,7 @@
         <v>1304.38</v>
       </c>
       <c r="K869" t="n">
-        <v>4223.86</v>
+        <v>4222.2</v>
       </c>
       <c r="L869" t="b">
         <v>0</v>
@@ -38385,7 +38385,7 @@
         <v>1260.9</v>
       </c>
       <c r="K870" t="n">
-        <v>4053.95</v>
+        <v>4052.32</v>
       </c>
       <c r="L870" t="b">
         <v>0</v>
@@ -38427,7 +38427,7 @@
         <v>1217.42</v>
       </c>
       <c r="K871" t="n">
-        <v>3879.41</v>
+        <v>3877.82</v>
       </c>
       <c r="L871" t="b">
         <v>0</v>
@@ -38469,7 +38469,7 @@
         <v>1173.94</v>
       </c>
       <c r="K872" t="n">
-        <v>3711.8</v>
+        <v>3710.27</v>
       </c>
       <c r="L872" t="b">
         <v>0</v>
@@ -38553,7 +38553,7 @@
         <v>1086.98</v>
       </c>
       <c r="K874" t="n">
-        <v>3378.09</v>
+        <v>3376.71</v>
       </c>
       <c r="L874" t="b">
         <v>0</v>
@@ -38637,7 +38637,7 @@
         <v>1000.02</v>
       </c>
       <c r="K876" t="n">
-        <v>3052.21</v>
+        <v>3050.96</v>
       </c>
       <c r="L876" t="b">
         <v>0</v>
@@ -38679,7 +38679,7 @@
         <v>956.54</v>
       </c>
       <c r="K877" t="n">
-        <v>2893.25</v>
+        <v>2892.07</v>
       </c>
       <c r="L877" t="b">
         <v>0</v>
@@ -38721,7 +38721,7 @@
         <v>913.0599999999999</v>
       </c>
       <c r="K878" t="n">
-        <v>2736.62</v>
+        <v>2735.47</v>
       </c>
       <c r="L878" t="b">
         <v>0</v>
@@ -38763,7 +38763,7 @@
         <v>869.59</v>
       </c>
       <c r="K879" t="n">
-        <v>2583.07</v>
+        <v>2581.95</v>
       </c>
       <c r="L879" t="b">
         <v>0</v>
@@ -38805,7 +38805,7 @@
         <v>826.11</v>
       </c>
       <c r="K880" t="n">
-        <v>2431.49</v>
+        <v>2430.43</v>
       </c>
       <c r="L880" t="b">
         <v>0</v>
@@ -38847,7 +38847,7 @@
         <v>782.63</v>
       </c>
       <c r="K881" t="n">
-        <v>2281.77</v>
+        <v>2280.73</v>
       </c>
       <c r="L881" t="b">
         <v>0</v>
@@ -38931,7 +38931,7 @@
         <v>695.67</v>
       </c>
       <c r="K883" t="n">
-        <v>1990.64</v>
+        <v>1989.7</v>
       </c>
       <c r="L883" t="b">
         <v>0</v>
@@ -39015,7 +39015,7 @@
         <v>608.71</v>
       </c>
       <c r="K885" t="n">
-        <v>1708.04</v>
+        <v>1707.18</v>
       </c>
       <c r="L885" t="b">
         <v>0</v>
@@ -39057,7 +39057,7 @@
         <v>565.23</v>
       </c>
       <c r="K886" t="n">
-        <v>1568.42</v>
+        <v>1567.63</v>
       </c>
       <c r="L886" t="b">
         <v>0</v>
@@ -39099,7 +39099,7 @@
         <v>521.75</v>
       </c>
       <c r="K887" t="n">
-        <v>1431.39</v>
+        <v>1430.64</v>
       </c>
       <c r="L887" t="b">
         <v>0</v>
@@ -39141,7 +39141,7 @@
         <v>478.27</v>
       </c>
       <c r="K888" t="n">
-        <v>1297.72</v>
+        <v>1297.04</v>
       </c>
       <c r="L888" t="b">
         <v>0</v>
@@ -39183,7 +39183,7 @@
         <v>434.79</v>
       </c>
       <c r="K889" t="n">
-        <v>1166.8</v>
+        <v>1166.19</v>
       </c>
       <c r="L889" t="b">
         <v>0</v>
@@ -39267,7 +39267,7 @@
         <v>347.83</v>
       </c>
       <c r="K891" t="n">
-        <v>913.08</v>
+        <v>912.6</v>
       </c>
       <c r="L891" t="b">
         <v>0</v>
@@ -39351,7 +39351,7 @@
         <v>260.88</v>
       </c>
       <c r="K893" t="n">
-        <v>670.5700000000001</v>
+        <v>670.22</v>
       </c>
       <c r="L893" t="b">
         <v>0</v>
@@ -39393,7 +39393,7 @@
         <v>217.4</v>
       </c>
       <c r="K894" t="n">
-        <v>552.6799999999999</v>
+        <v>552.39</v>
       </c>
       <c r="L894" t="b">
         <v>0</v>
@@ -39519,7 +39519,7 @@
         <v>86.95999999999999</v>
       </c>
       <c r="K897" t="n">
-        <v>213.88</v>
+        <v>213.77</v>
       </c>
       <c r="L897" t="b">
         <v>0</v>
@@ -39603,7 +39603,7 @@
         <v>535.5599999999999</v>
       </c>
       <c r="K899" t="n">
-        <v>2370.69</v>
+        <v>2369.74</v>
       </c>
       <c r="L899" t="b">
         <v>1</v>
@@ -39729,7 +39729,7 @@
         <v>535.5599999999999</v>
       </c>
       <c r="K902" t="n">
-        <v>2312.34</v>
+        <v>2311.41</v>
       </c>
       <c r="L902" t="b">
         <v>0</v>
@@ -39771,7 +39771,7 @@
         <v>520.6799999999999</v>
       </c>
       <c r="K903" t="n">
-        <v>2228.31</v>
+        <v>2227.42</v>
       </c>
       <c r="L903" t="b">
         <v>0</v>
@@ -39813,7 +39813,7 @@
         <v>505.81</v>
       </c>
       <c r="K904" t="n">
-        <v>2144.85</v>
+        <v>2143.95</v>
       </c>
       <c r="L904" t="b">
         <v>0</v>
@@ -39855,7 +39855,7 @@
         <v>490.93</v>
       </c>
       <c r="K905" t="n">
-        <v>2065.82</v>
+        <v>2064.92</v>
       </c>
       <c r="L905" t="b">
         <v>0</v>
@@ -39981,7 +39981,7 @@
         <v>446.3</v>
       </c>
       <c r="K908" t="n">
-        <v>1825.41</v>
+        <v>1824.58</v>
       </c>
       <c r="L908" t="b">
         <v>0</v>
@@ -40065,7 +40065,7 @@
         <v>416.55</v>
       </c>
       <c r="K910" t="n">
-        <v>1671.15</v>
+        <v>1670.37</v>
       </c>
       <c r="L910" t="b">
         <v>0</v>
@@ -40107,7 +40107,7 @@
         <v>401.67</v>
       </c>
       <c r="K911" t="n">
-        <v>1595.37</v>
+        <v>1594.66</v>
       </c>
       <c r="L911" t="b">
         <v>0</v>
@@ -40149,7 +40149,7 @@
         <v>386.79</v>
       </c>
       <c r="K912" t="n">
-        <v>1522.63</v>
+        <v>1521.95</v>
       </c>
       <c r="L912" t="b">
         <v>0</v>
@@ -40191,7 +40191,7 @@
         <v>371.92</v>
       </c>
       <c r="K913" t="n">
-        <v>1451.5</v>
+        <v>1450.88</v>
       </c>
       <c r="L913" t="b">
         <v>0</v>
@@ -40233,7 +40233,7 @@
         <v>357.04</v>
       </c>
       <c r="K914" t="n">
-        <v>1380.64</v>
+        <v>1380.08</v>
       </c>
       <c r="L914" t="b">
         <v>0</v>
@@ -40317,7 +40317,7 @@
         <v>327.29</v>
       </c>
       <c r="K916" t="n">
-        <v>1243.38</v>
+        <v>1242.89</v>
       </c>
       <c r="L916" t="b">
         <v>0</v>
@@ -40359,7 +40359,7 @@
         <v>312.41</v>
       </c>
       <c r="K917" t="n">
-        <v>1178.23</v>
+        <v>1177.8</v>
       </c>
       <c r="L917" t="b">
         <v>0</v>
@@ -40443,7 +40443,7 @@
         <v>282.66</v>
       </c>
       <c r="K919" t="n">
-        <v>1050.68</v>
+        <v>1050.32</v>
       </c>
       <c r="L919" t="b">
         <v>0</v>
@@ -40569,7 +40569,7 @@
         <v>238.03</v>
       </c>
       <c r="K922" t="n">
-        <v>866.8099999999999</v>
+        <v>866.55</v>
       </c>
       <c r="L922" t="b">
         <v>0</v>
@@ -40611,7 +40611,7 @@
         <v>223.15</v>
       </c>
       <c r="K923" t="n">
-        <v>807.67</v>
+        <v>807.4400000000001</v>
       </c>
       <c r="L923" t="b">
         <v>0</v>
@@ -40653,7 +40653,7 @@
         <v>208.27</v>
       </c>
       <c r="K924" t="n">
-        <v>749.58</v>
+        <v>749.38</v>
       </c>
       <c r="L924" t="b">
         <v>0</v>
@@ -40695,7 +40695,7 @@
         <v>193.4</v>
       </c>
       <c r="K925" t="n">
-        <v>692.05</v>
+        <v>691.86</v>
       </c>
       <c r="L925" t="b">
         <v>0</v>
@@ -40737,7 +40737,7 @@
         <v>178.52</v>
       </c>
       <c r="K926" t="n">
-        <v>635.16</v>
+        <v>634.99</v>
       </c>
       <c r="L926" t="b">
         <v>0</v>
@@ -40779,7 +40779,7 @@
         <v>163.64</v>
       </c>
       <c r="K927" t="n">
-        <v>579.05</v>
+        <v>578.89</v>
       </c>
       <c r="L927" t="b">
         <v>0</v>
@@ -40905,7 +40905,7 @@
         <v>119.01</v>
       </c>
       <c r="K930" t="n">
-        <v>414.16</v>
+        <v>414.05</v>
       </c>
       <c r="L930" t="b">
         <v>0</v>
@@ -40947,7 +40947,7 @@
         <v>104.14</v>
       </c>
       <c r="K931" t="n">
-        <v>360.25</v>
+        <v>360.14</v>
       </c>
       <c r="L931" t="b">
         <v>0</v>
@@ -40989,7 +40989,7 @@
         <v>89.26000000000001</v>
       </c>
       <c r="K932" t="n">
-        <v>306.89</v>
+        <v>306.8</v>
       </c>
       <c r="L932" t="b">
         <v>0</v>
@@ -41031,7 +41031,7 @@
         <v>74.38</v>
       </c>
       <c r="K933" t="n">
-        <v>254.11</v>
+        <v>254.03</v>
       </c>
       <c r="L933" t="b">
         <v>0</v>
@@ -41073,7 +41073,7 @@
         <v>59.51</v>
       </c>
       <c r="K934" t="n">
-        <v>201.8</v>
+        <v>201.73</v>
       </c>
       <c r="L934" t="b">
         <v>0</v>
@@ -41157,7 +41157,7 @@
         <v>29.75</v>
       </c>
       <c r="K936" t="n">
-        <v>99.45</v>
+        <v>99.42</v>
       </c>
       <c r="L936" t="b">
         <v>0</v>
@@ -41325,7 +41325,7 @@
         <v>1065.77</v>
       </c>
       <c r="K940" t="n">
-        <v>4601.56</v>
+        <v>4599.71</v>
       </c>
       <c r="L940" t="b">
         <v>1</v>
@@ -41367,7 +41367,7 @@
         <v>1065.77</v>
       </c>
       <c r="K941" t="n">
-        <v>4561.04</v>
+        <v>4559.21</v>
       </c>
       <c r="L941" t="b">
         <v>1</v>
@@ -41409,7 +41409,7 @@
         <v>1065.77</v>
       </c>
       <c r="K942" t="n">
-        <v>4519.33</v>
+        <v>4517.43</v>
       </c>
       <c r="L942" t="b">
         <v>1</v>
@@ -41451,7 +41451,7 @@
         <v>1065.77</v>
       </c>
       <c r="K943" t="n">
-        <v>4484.71</v>
+        <v>4482.75</v>
       </c>
       <c r="L943" t="b">
         <v>1</v>
@@ -41577,7 +41577,7 @@
         <v>1021.36</v>
       </c>
       <c r="K946" t="n">
-        <v>4177.45</v>
+        <v>4175.55</v>
       </c>
       <c r="L946" t="b">
         <v>0</v>
@@ -41661,7 +41661,7 @@
         <v>976.95</v>
       </c>
       <c r="K948" t="n">
-        <v>3919.44</v>
+        <v>3917.62</v>
       </c>
       <c r="L948" t="b">
         <v>0</v>
@@ -41703,7 +41703,7 @@
         <v>954.75</v>
       </c>
       <c r="K949" t="n">
-        <v>3792.11</v>
+        <v>3790.41</v>
       </c>
       <c r="L949" t="b">
         <v>0</v>
@@ -41745,7 +41745,7 @@
         <v>932.55</v>
       </c>
       <c r="K950" t="n">
-        <v>3671.01</v>
+        <v>3669.38</v>
       </c>
       <c r="L950" t="b">
         <v>0</v>
@@ -41787,7 +41787,7 @@
         <v>910.34</v>
       </c>
       <c r="K951" t="n">
-        <v>3552.85</v>
+        <v>3551.32</v>
       </c>
       <c r="L951" t="b">
         <v>0</v>
@@ -41829,7 +41829,7 @@
         <v>888.14</v>
       </c>
       <c r="K952" t="n">
-        <v>3434.35</v>
+        <v>3432.94</v>
       </c>
       <c r="L952" t="b">
         <v>0</v>
@@ -41913,7 +41913,7 @@
         <v>843.73</v>
       </c>
       <c r="K954" t="n">
-        <v>3205.37</v>
+        <v>3204.12</v>
       </c>
       <c r="L954" t="b">
         <v>0</v>
@@ -41955,7 +41955,7 @@
         <v>821.53</v>
       </c>
       <c r="K955" t="n">
-        <v>3098.33</v>
+        <v>3097.2</v>
       </c>
       <c r="L955" t="b">
         <v>0</v>
@@ -42039,7 +42039,7 @@
         <v>777.12</v>
       </c>
       <c r="K957" t="n">
-        <v>2888.67</v>
+        <v>2887.69</v>
       </c>
       <c r="L957" t="b">
         <v>0</v>
@@ -42165,7 +42165,7 @@
         <v>710.51</v>
       </c>
       <c r="K960" t="n">
-        <v>2587.42</v>
+        <v>2586.64</v>
       </c>
       <c r="L960" t="b">
         <v>0</v>
@@ -42207,7 +42207,7 @@
         <v>688.3099999999999</v>
       </c>
       <c r="K961" t="n">
-        <v>2491.25</v>
+        <v>2490.55</v>
       </c>
       <c r="L961" t="b">
         <v>0</v>
@@ -42249,7 +42249,7 @@
         <v>666.1</v>
       </c>
       <c r="K962" t="n">
-        <v>2397.33</v>
+        <v>2396.68</v>
       </c>
       <c r="L962" t="b">
         <v>0</v>
@@ -42291,7 +42291,7 @@
         <v>643.9</v>
       </c>
       <c r="K963" t="n">
-        <v>2304.14</v>
+        <v>2303.51</v>
       </c>
       <c r="L963" t="b">
         <v>0</v>
@@ -42333,7 +42333,7 @@
         <v>621.7</v>
       </c>
       <c r="K964" t="n">
-        <v>2211.94</v>
+        <v>2211.34</v>
       </c>
       <c r="L964" t="b">
         <v>0</v>
@@ -42375,7 +42375,7 @@
         <v>599.49</v>
       </c>
       <c r="K965" t="n">
-        <v>2121.29</v>
+        <v>2120.72</v>
       </c>
       <c r="L965" t="b">
         <v>0</v>
@@ -42501,7 +42501,7 @@
         <v>532.88</v>
       </c>
       <c r="K968" t="n">
-        <v>1854.4</v>
+        <v>1853.89</v>
       </c>
       <c r="L968" t="b">
         <v>0</v>
@@ -42543,7 +42543,7 @@
         <v>510.68</v>
       </c>
       <c r="K969" t="n">
-        <v>1766.62</v>
+        <v>1766.12</v>
       </c>
       <c r="L969" t="b">
         <v>0</v>
@@ -42585,7 +42585,7 @@
         <v>488.48</v>
       </c>
       <c r="K970" t="n">
-        <v>1679.45</v>
+        <v>1678.94</v>
       </c>
       <c r="L970" t="b">
         <v>0</v>
@@ -42627,7 +42627,7 @@
         <v>466.27</v>
       </c>
       <c r="K971" t="n">
-        <v>1592.89</v>
+        <v>1592.39</v>
       </c>
       <c r="L971" t="b">
         <v>0</v>
@@ -42669,7 +42669,7 @@
         <v>444.07</v>
       </c>
       <c r="K972" t="n">
-        <v>1505.92</v>
+        <v>1505.43</v>
       </c>
       <c r="L972" t="b">
         <v>0</v>
@@ -42753,7 +42753,7 @@
         <v>399.66</v>
       </c>
       <c r="K974" t="n">
-        <v>1335.87</v>
+        <v>1335.4</v>
       </c>
       <c r="L974" t="b">
         <v>0</v>
@@ -42879,7 +42879,7 @@
         <v>333.05</v>
       </c>
       <c r="K977" t="n">
-        <v>1087.85</v>
+        <v>1087.43</v>
       </c>
       <c r="L977" t="b">
         <v>0</v>
@@ -42921,7 +42921,7 @@
         <v>310.85</v>
       </c>
       <c r="K978" t="n">
-        <v>1006.6</v>
+        <v>1006.2</v>
       </c>
       <c r="L978" t="b">
         <v>0</v>
@@ -42963,7 +42963,7 @@
         <v>288.65</v>
       </c>
       <c r="K979" t="n">
-        <v>928.03</v>
+        <v>927.66</v>
       </c>
       <c r="L979" t="b">
         <v>0</v>
@@ -43005,7 +43005,7 @@
         <v>266.44</v>
       </c>
       <c r="K980" t="n">
-        <v>849.04</v>
+        <v>848.6900000000001</v>
       </c>
       <c r="L980" t="b">
         <v>0</v>
@@ -43047,7 +43047,7 @@
         <v>244.24</v>
       </c>
       <c r="K981" t="n">
-        <v>772.24</v>
+        <v>771.92</v>
       </c>
       <c r="L981" t="b">
         <v>0</v>
@@ -43131,7 +43131,7 @@
         <v>199.83</v>
       </c>
       <c r="K983" t="n">
-        <v>621.03</v>
+        <v>620.78</v>
       </c>
       <c r="L983" t="b">
         <v>0</v>
@@ -43215,7 +43215,7 @@
         <v>155.42</v>
       </c>
       <c r="K985" t="n">
-        <v>474.38</v>
+        <v>474.18</v>
       </c>
       <c r="L985" t="b">
         <v>0</v>
@@ -43257,7 +43257,7 @@
         <v>133.22</v>
       </c>
       <c r="K986" t="n">
-        <v>402.95</v>
+        <v>402.79</v>
       </c>
       <c r="L986" t="b">
         <v>0</v>
@@ -43299,7 +43299,7 @@
         <v>111.02</v>
       </c>
       <c r="K987" t="n">
-        <v>332.74</v>
+        <v>332.6</v>
       </c>
       <c r="L987" t="b">
         <v>0</v>
@@ -43341,7 +43341,7 @@
         <v>88.81</v>
       </c>
       <c r="K988" t="n">
-        <v>263.82</v>
+        <v>263.7</v>
       </c>
       <c r="L988" t="b">
         <v>0</v>
@@ -43383,7 +43383,7 @@
         <v>66.61</v>
       </c>
       <c r="K989" t="n">
-        <v>196.06</v>
+        <v>195.97</v>
       </c>
       <c r="L989" t="b">
         <v>0</v>
@@ -43425,7 +43425,7 @@
         <v>44.41</v>
       </c>
       <c r="K990" t="n">
-        <v>129.47</v>
+        <v>129.41</v>
       </c>
       <c r="L990" t="b">
         <v>0</v>
@@ -43551,7 +43551,7 @@
         <v>1600.17</v>
       </c>
       <c r="K993" t="n">
-        <v>6908.89</v>
+        <v>6906.12</v>
       </c>
       <c r="L993" t="b">
         <v>1</v>
@@ -43593,7 +43593,7 @@
         <v>1600.17</v>
       </c>
       <c r="K994" t="n">
-        <v>6848.05</v>
+        <v>6845.3</v>
       </c>
       <c r="L994" t="b">
         <v>1</v>
@@ -43635,7 +43635,7 @@
         <v>1600.17</v>
       </c>
       <c r="K995" t="n">
-        <v>6785.43</v>
+        <v>6782.58</v>
       </c>
       <c r="L995" t="b">
         <v>1</v>
@@ -43677,7 +43677,7 @@
         <v>1600.17</v>
       </c>
       <c r="K996" t="n">
-        <v>6733.46</v>
+        <v>6730.51</v>
       </c>
       <c r="L996" t="b">
         <v>1</v>
@@ -43803,7 +43803,7 @@
         <v>1573.5</v>
       </c>
       <c r="K999" t="n">
-        <v>6435.75</v>
+        <v>6432.81</v>
       </c>
       <c r="L999" t="b">
         <v>0</v>
@@ -43887,7 +43887,7 @@
         <v>1520.16</v>
       </c>
       <c r="K1001" t="n">
-        <v>6098.74</v>
+        <v>6095.9</v>
       </c>
       <c r="L1001" t="b">
         <v>0</v>
@@ -43929,7 +43929,7 @@
         <v>1493.49</v>
       </c>
       <c r="K1002" t="n">
-        <v>5931.9</v>
+        <v>5929.25</v>
       </c>
       <c r="L1002" t="b">
         <v>0</v>
@@ -43971,7 +43971,7 @@
         <v>1466.82</v>
       </c>
       <c r="K1003" t="n">
-        <v>5774.21</v>
+        <v>5771.63</v>
       </c>
       <c r="L1003" t="b">
         <v>0</v>
@@ -44013,7 +44013,7 @@
         <v>1440.15</v>
       </c>
       <c r="K1004" t="n">
-        <v>5620.56</v>
+        <v>5618.15</v>
       </c>
       <c r="L1004" t="b">
         <v>0</v>
@@ -44055,7 +44055,7 @@
         <v>1413.48</v>
       </c>
       <c r="K1005" t="n">
-        <v>5465.8</v>
+        <v>5463.56</v>
       </c>
       <c r="L1005" t="b">
         <v>0</v>
@@ -44139,7 +44139,7 @@
         <v>1360.14</v>
       </c>
       <c r="K1007" t="n">
-        <v>5167.24</v>
+        <v>5165.21</v>
       </c>
       <c r="L1007" t="b">
         <v>0</v>
@@ -44181,7 +44181,7 @@
         <v>1333.47</v>
       </c>
       <c r="K1008" t="n">
-        <v>5029.09</v>
+        <v>5027.25</v>
       </c>
       <c r="L1008" t="b">
         <v>0</v>
@@ -44265,7 +44265,7 @@
         <v>1280.14</v>
       </c>
       <c r="K1010" t="n">
-        <v>4758.44</v>
+        <v>4756.83</v>
       </c>
       <c r="L1010" t="b">
         <v>0</v>
@@ -44391,7 +44391,7 @@
         <v>1200.13</v>
       </c>
       <c r="K1013" t="n">
-        <v>4370.41</v>
+        <v>4369.1</v>
       </c>
       <c r="L1013" t="b">
         <v>0</v>
@@ -44433,7 +44433,7 @@
         <v>1173.46</v>
       </c>
       <c r="K1014" t="n">
-        <v>4247.2</v>
+        <v>4245.99</v>
       </c>
       <c r="L1014" t="b">
         <v>0</v>
@@ -44475,7 +44475,7 @@
         <v>1146.79</v>
       </c>
       <c r="K1015" t="n">
-        <v>4127.33</v>
+        <v>4126.2</v>
       </c>
       <c r="L1015" t="b">
         <v>0</v>
@@ -44517,7 +44517,7 @@
         <v>1120.12</v>
       </c>
       <c r="K1016" t="n">
-        <v>4008.24</v>
+        <v>4007.14</v>
       </c>
       <c r="L1016" t="b">
         <v>0</v>
@@ -44559,7 +44559,7 @@
         <v>1093.45</v>
       </c>
       <c r="K1017" t="n">
-        <v>3890.39</v>
+        <v>3889.33</v>
       </c>
       <c r="L1017" t="b">
         <v>0</v>
@@ -44601,7 +44601,7 @@
         <v>1066.78</v>
       </c>
       <c r="K1018" t="n">
-        <v>3774.77</v>
+        <v>3773.74</v>
       </c>
       <c r="L1018" t="b">
         <v>0</v>
@@ -44727,7 +44727,7 @@
         <v>986.77</v>
       </c>
       <c r="K1021" t="n">
-        <v>3433.89</v>
+        <v>3432.95</v>
       </c>
       <c r="L1021" t="b">
         <v>0</v>
@@ -44769,7 +44769,7 @@
         <v>960.1</v>
       </c>
       <c r="K1022" t="n">
-        <v>3321.32</v>
+        <v>3320.38</v>
       </c>
       <c r="L1022" t="b">
         <v>0</v>
@@ -44811,7 +44811,7 @@
         <v>933.4299999999999</v>
       </c>
       <c r="K1023" t="n">
-        <v>3209.26</v>
+        <v>3208.29</v>
       </c>
       <c r="L1023" t="b">
         <v>0</v>
@@ -44853,7 +44853,7 @@
         <v>906.76</v>
       </c>
       <c r="K1024" t="n">
-        <v>3097.7</v>
+        <v>3096.71</v>
       </c>
       <c r="L1024" t="b">
         <v>0</v>
@@ -44895,7 +44895,7 @@
         <v>880.09</v>
       </c>
       <c r="K1025" t="n">
-        <v>2984.54</v>
+        <v>2983.59</v>
       </c>
       <c r="L1025" t="b">
         <v>0</v>
@@ -44979,7 +44979,7 @@
         <v>826.75</v>
       </c>
       <c r="K1027" t="n">
-        <v>2763.42</v>
+        <v>2762.44</v>
       </c>
       <c r="L1027" t="b">
         <v>0</v>
@@ -45105,7 +45105,7 @@
         <v>746.75</v>
       </c>
       <c r="K1030" t="n">
-        <v>2439.1</v>
+        <v>2438.15</v>
       </c>
       <c r="L1030" t="b">
         <v>0</v>
@@ -45147,7 +45147,7 @@
         <v>720.08</v>
       </c>
       <c r="K1031" t="n">
-        <v>2331.76</v>
+        <v>2330.85</v>
       </c>
       <c r="L1031" t="b">
         <v>0</v>
@@ -45189,7 +45189,7 @@
         <v>693.41</v>
       </c>
       <c r="K1032" t="n">
-        <v>2229.39</v>
+        <v>2228.49</v>
       </c>
       <c r="L1032" t="b">
         <v>0</v>
@@ -45231,7 +45231,7 @@
         <v>666.74</v>
       </c>
       <c r="K1033" t="n">
-        <v>2124.62</v>
+        <v>2123.74</v>
       </c>
       <c r="L1033" t="b">
         <v>0</v>
@@ -45273,7 +45273,7 @@
         <v>640.0700000000001</v>
       </c>
       <c r="K1034" t="n">
-        <v>2023.78</v>
+        <v>2022.95</v>
       </c>
       <c r="L1034" t="b">
         <v>0</v>
@@ -45357,7 +45357,7 @@
         <v>586.73</v>
       </c>
       <c r="K1036" t="n">
-        <v>1823.42</v>
+        <v>1822.67</v>
       </c>
       <c r="L1036" t="b">
         <v>0</v>
@@ -45441,7 +45441,7 @@
         <v>533.39</v>
       </c>
       <c r="K1038" t="n">
-        <v>1627.98</v>
+        <v>1627.31</v>
       </c>
       <c r="L1038" t="b">
         <v>0</v>
@@ -45483,7 +45483,7 @@
         <v>506.72</v>
       </c>
       <c r="K1039" t="n">
-        <v>1532.67</v>
+        <v>1532.05</v>
       </c>
       <c r="L1039" t="b">
         <v>0</v>
@@ -45525,7 +45525,7 @@
         <v>480.05</v>
       </c>
       <c r="K1040" t="n">
-        <v>1438.8</v>
+        <v>1438.19</v>
       </c>
       <c r="L1040" t="b">
         <v>0</v>
@@ -45567,7 +45567,7 @@
         <v>453.38</v>
       </c>
       <c r="K1041" t="n">
-        <v>1346.75</v>
+        <v>1346.17</v>
       </c>
       <c r="L1041" t="b">
         <v>0</v>
@@ -45609,7 +45609,7 @@
         <v>426.71</v>
       </c>
       <c r="K1042" t="n">
-        <v>1255.95</v>
+        <v>1255.4</v>
       </c>
       <c r="L1042" t="b">
         <v>0</v>
@@ -45651,7 +45651,7 @@
         <v>400.04</v>
       </c>
       <c r="K1043" t="n">
-        <v>1166.34</v>
+        <v>1165.8</v>
       </c>
       <c r="L1043" t="b">
         <v>0</v>
@@ -45735,7 +45735,7 @@
         <v>346.7</v>
       </c>
       <c r="K1045" t="n">
-        <v>992.08</v>
+        <v>991.62</v>
       </c>
       <c r="L1045" t="b">
         <v>0</v>
@@ -45819,7 +45819,7 @@
         <v>293.36</v>
       </c>
       <c r="K1047" t="n">
-        <v>823.1799999999999</v>
+        <v>822.76</v>
       </c>
       <c r="L1047" t="b">
         <v>0</v>
@@ -45861,7 +45861,7 @@
         <v>266.69</v>
       </c>
       <c r="K1048" t="n">
-        <v>740.03</v>
+        <v>739.66</v>
       </c>
       <c r="L1048" t="b">
         <v>0</v>
@@ -45903,7 +45903,7 @@
         <v>240.03</v>
       </c>
       <c r="K1049" t="n">
-        <v>658.5</v>
+        <v>658.15</v>
       </c>
       <c r="L1049" t="b">
         <v>0</v>
@@ -45945,7 +45945,7 @@
         <v>213.36</v>
       </c>
       <c r="K1050" t="n">
-        <v>578.91</v>
+        <v>578.61</v>
       </c>
       <c r="L1050" t="b">
         <v>0</v>
@@ -45987,7 +45987,7 @@
         <v>186.69</v>
       </c>
       <c r="K1051" t="n">
-        <v>500.99</v>
+        <v>500.73</v>
       </c>
       <c r="L1051" t="b">
         <v>0</v>
@@ -46071,7 +46071,7 @@
         <v>133.35</v>
       </c>
       <c r="K1053" t="n">
-        <v>350.04</v>
+        <v>349.86</v>
       </c>
       <c r="L1053" t="b">
         <v>0</v>
@@ -46155,7 +46155,7 @@
         <v>80.01000000000001</v>
       </c>
       <c r="K1055" t="n">
-        <v>205.66</v>
+        <v>205.55</v>
       </c>
       <c r="L1055" t="b">
         <v>0</v>
@@ -46197,7 +46197,7 @@
         <v>53.34</v>
       </c>
       <c r="K1056" t="n">
-        <v>135.6</v>
+        <v>135.53</v>
       </c>
       <c r="L1056" t="b">
         <v>0</v>
@@ -46281,7 +46281,7 @@
         <v>712.8099999999999</v>
       </c>
       <c r="K1058" t="n">
-        <v>3077.62</v>
+        <v>3076.38</v>
       </c>
       <c r="L1058" t="b">
         <v>0</v>
@@ -46323,7 +46323,7 @@
         <v>697.96</v>
       </c>
       <c r="K1059" t="n">
-        <v>2986.97</v>
+        <v>2985.77</v>
       </c>
       <c r="L1059" t="b">
         <v>0</v>
@@ -46365,7 +46365,7 @@
         <v>683.11</v>
       </c>
       <c r="K1060" t="n">
-        <v>2896.68</v>
+        <v>2895.46</v>
       </c>
       <c r="L1060" t="b">
         <v>0</v>
@@ -46407,7 +46407,7 @@
         <v>668.26</v>
       </c>
       <c r="K1061" t="n">
-        <v>2812</v>
+        <v>2810.77</v>
       </c>
       <c r="L1061" t="b">
         <v>0</v>
@@ -46533,7 +46533,7 @@
         <v>623.71</v>
       </c>
       <c r="K1064" t="n">
-        <v>2551.01</v>
+        <v>2549.85</v>
       </c>
       <c r="L1064" t="b">
         <v>0</v>
@@ -46617,7 +46617,7 @@
         <v>594.01</v>
       </c>
       <c r="K1066" t="n">
-        <v>2383.1</v>
+        <v>2381.99</v>
       </c>
       <c r="L1066" t="b">
         <v>0</v>
@@ -46659,7 +46659,7 @@
         <v>579.16</v>
       </c>
       <c r="K1067" t="n">
-        <v>2300.31</v>
+        <v>2299.28</v>
       </c>
       <c r="L1067" t="b">
         <v>0</v>
@@ -46701,7 +46701,7 @@
         <v>564.3099999999999</v>
       </c>
       <c r="K1068" t="n">
-        <v>2221.42</v>
+        <v>2220.43</v>
       </c>
       <c r="L1068" t="b">
         <v>0</v>
@@ -46743,7 +46743,7 @@
         <v>549.46</v>
       </c>
       <c r="K1069" t="n">
-        <v>2144.39</v>
+        <v>2143.47</v>
       </c>
       <c r="L1069" t="b">
         <v>0</v>
@@ -46785,7 +46785,7 @@
         <v>534.61</v>
       </c>
       <c r="K1070" t="n">
-        <v>2067.27</v>
+        <v>2066.42</v>
       </c>
       <c r="L1070" t="b">
         <v>0</v>
@@ -46869,7 +46869,7 @@
         <v>504.91</v>
       </c>
       <c r="K1072" t="n">
-        <v>1918.16</v>
+        <v>1917.4</v>
       </c>
       <c r="L1072" t="b">
         <v>0</v>
@@ -46911,7 +46911,7 @@
         <v>490.06</v>
       </c>
       <c r="K1073" t="n">
-        <v>1848.2</v>
+        <v>1847.53</v>
       </c>
       <c r="L1073" t="b">
         <v>0</v>
@@ -46995,7 +46995,7 @@
         <v>460.36</v>
       </c>
       <c r="K1075" t="n">
-        <v>1711.2</v>
+        <v>1710.62</v>
       </c>
       <c r="L1075" t="b">
         <v>0</v>
@@ -47121,7 +47121,7 @@
         <v>415.8</v>
       </c>
       <c r="K1078" t="n">
-        <v>1514.2</v>
+        <v>1513.75</v>
       </c>
       <c r="L1078" t="b">
         <v>0</v>
@@ -47163,7 +47163,7 @@
         <v>400.95</v>
       </c>
       <c r="K1079" t="n">
-        <v>1451.21</v>
+        <v>1450.8</v>
       </c>
       <c r="L1079" t="b">
         <v>0</v>
@@ -47205,7 +47205,7 @@
         <v>386.1</v>
       </c>
       <c r="K1080" t="n">
-        <v>1389.6</v>
+        <v>1389.22</v>
       </c>
       <c r="L1080" t="b">
         <v>0</v>
@@ -47247,7 +47247,7 @@
         <v>371.25</v>
       </c>
       <c r="K1081" t="n">
-        <v>1328.5</v>
+        <v>1328.13</v>
       </c>
       <c r="L1081" t="b">
         <v>0</v>
@@ -47289,7 +47289,7 @@
         <v>356.4</v>
       </c>
       <c r="K1082" t="n">
-        <v>1268.05</v>
+        <v>1267.71</v>
       </c>
       <c r="L1082" t="b">
         <v>0</v>
@@ -47331,7 +47331,7 @@
         <v>341.55</v>
       </c>
       <c r="K1083" t="n">
-        <v>1208.58</v>
+        <v>1208.25</v>
       </c>
       <c r="L1083" t="b">
         <v>0</v>
@@ -47457,7 +47457,7 @@
         <v>297</v>
       </c>
       <c r="K1086" t="n">
-        <v>1033.55</v>
+        <v>1033.27</v>
       </c>
       <c r="L1086" t="b">
         <v>0</v>
@@ -47499,7 +47499,7 @@
         <v>282.15</v>
       </c>
       <c r="K1087" t="n">
-        <v>976.0599999999999</v>
+        <v>975.79</v>
       </c>
       <c r="L1087" t="b">
         <v>0</v>
@@ -47541,7 +47541,7 @@
         <v>267.3</v>
       </c>
       <c r="K1088" t="n">
-        <v>919.02</v>
+        <v>918.74</v>
       </c>
       <c r="L1088" t="b">
         <v>0</v>
@@ -47583,7 +47583,7 @@
         <v>252.45</v>
       </c>
       <c r="K1089" t="n">
-        <v>862.4400000000001</v>
+        <v>862.16</v>
       </c>
       <c r="L1089" t="b">
         <v>0</v>
@@ -47625,7 +47625,7 @@
         <v>237.6</v>
       </c>
       <c r="K1090" t="n">
-        <v>805.75</v>
+        <v>805.49</v>
       </c>
       <c r="L1090" t="b">
         <v>0</v>
@@ -47709,7 +47709,7 @@
         <v>207.9</v>
       </c>
       <c r="K1092" t="n">
-        <v>694.91</v>
+        <v>694.66</v>
       </c>
       <c r="L1092" t="b">
         <v>0</v>
@@ -47835,7 +47835,7 @@
         <v>163.35</v>
       </c>
       <c r="K1095" t="n">
-        <v>533.5599999999999</v>
+        <v>533.35</v>
       </c>
       <c r="L1095" t="b">
         <v>0</v>
@@ -47877,7 +47877,7 @@
         <v>148.5</v>
       </c>
       <c r="K1096" t="n">
-        <v>480.88</v>
+        <v>480.69</v>
       </c>
       <c r="L1096" t="b">
         <v>0</v>
@@ -47919,7 +47919,7 @@
         <v>133.65</v>
       </c>
       <c r="K1097" t="n">
-        <v>429.71</v>
+        <v>429.53</v>
       </c>
       <c r="L1097" t="b">
         <v>0</v>
@@ -47961,7 +47961,7 @@
         <v>118.8</v>
       </c>
       <c r="K1098" t="n">
-        <v>378.57</v>
+        <v>378.42</v>
       </c>
       <c r="L1098" t="b">
         <v>0</v>
@@ -48003,7 +48003,7 @@
         <v>103.95</v>
       </c>
       <c r="K1099" t="n">
-        <v>328.68</v>
+        <v>328.54</v>
       </c>
       <c r="L1099" t="b">
         <v>0</v>
@@ -48087,7 +48087,7 @@
         <v>74.25</v>
       </c>
       <c r="K1101" t="n">
-        <v>230.75</v>
+        <v>230.66</v>
       </c>
       <c r="L1101" t="b">
         <v>0</v>
@@ -48171,7 +48171,7 @@
         <v>44.55</v>
       </c>
       <c r="K1103" t="n">
-        <v>135.97</v>
+        <v>135.92</v>
       </c>
       <c r="L1103" t="b">
         <v>0</v>
@@ -48213,7 +48213,7 @@
         <v>29.7</v>
       </c>
       <c r="K1104" t="n">
-        <v>89.83</v>
+        <v>89.8</v>
       </c>
       <c r="L1104" t="b">
         <v>0</v>
@@ -48255,7 +48255,7 @@
         <v>14.85</v>
       </c>
       <c r="K1105" t="n">
-        <v>44.51</v>
+        <v>44.49</v>
       </c>
       <c r="L1105" t="b">
         <v>0</v>

--- a/output/fluxos_amostra.xlsx
+++ b/output/fluxos_amostra.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fator ContAgil (bacen:sgs.11)</t>
+          <t>fator ContAgil (stp:/workspace/data/selic_fatores_bacen.xlsx)</t>
         </is>
       </c>
     </row>
